--- a/artfynd/A 29563-2025 artfynd.xlsx
+++ b/artfynd/A 29563-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1190,45 +1190,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129401658</v>
+        <v>129410985</v>
       </c>
       <c r="B7" t="n">
-        <v>79041</v>
+        <v>97577</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>559658</v>
+        <v>559661</v>
       </c>
       <c r="R7" t="n">
-        <v>7063991</v>
+        <v>7063971</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1258,19 +1258,9 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>11:59</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>11:59</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1285,12 +1275,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1300,7 +1290,7 @@
         <v>129402383</v>
       </c>
       <c r="B8" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1413,45 +1403,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129410985</v>
+        <v>129401658</v>
       </c>
       <c r="B9" t="n">
-        <v>97576</v>
+        <v>79041</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>559661</v>
+        <v>559658</v>
       </c>
       <c r="R9" t="n">
-        <v>7063971</v>
+        <v>7063991</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1481,9 +1471,19 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1498,12 +1498,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1818,6 +1818,2782 @@
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>129425378</v>
+      </c>
+      <c r="B13" t="n">
+        <v>91993</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Spångmyran, Spångmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>559596</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7063994</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>129425867</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Mattismyrberget, Mattismyrberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>559534</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7064000</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>15:23</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>15:23</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>129425271</v>
+      </c>
+      <c r="B15" t="n">
+        <v>91560</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Mattismyrberget, Mattismyrberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>559486</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7064108</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>14:44</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>14:44</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>129427236</v>
+      </c>
+      <c r="B16" t="n">
+        <v>91504</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Mattismyrberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>559485</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7064097</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>129425134</v>
+      </c>
+      <c r="B17" t="n">
+        <v>82873</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Mattismyrberget, Mattismyrberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>559416</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7064110</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>129427262</v>
+      </c>
+      <c r="B18" t="n">
+        <v>80146</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Mattismyrberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>559585</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7064050</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>129427253</v>
+      </c>
+      <c r="B19" t="n">
+        <v>91993</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Mattismyrberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>559571</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7064007</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>129427230</v>
+      </c>
+      <c r="B20" t="n">
+        <v>83007</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Mattismyrberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>559425</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7064125</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>129425894</v>
+      </c>
+      <c r="B21" t="n">
+        <v>82873</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Spångmyran, Spångmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>559542</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7064008</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>129427255</v>
+      </c>
+      <c r="B22" t="n">
+        <v>91838</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>658</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Mattismyrberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>559572</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7064006</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>129425250</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57724</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Mattismyrberget, Mattismyrberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>559469</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7064105</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>129427280</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Mattismyrberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>559416</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7064119</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>129427251</v>
+      </c>
+      <c r="B25" t="n">
+        <v>80147</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Mattismyrberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>559590</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7064053</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>129427261</v>
+      </c>
+      <c r="B26" t="n">
+        <v>80146</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Mattismyrberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>559580</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7064063</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>129425698</v>
+      </c>
+      <c r="B27" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Mattismyrberget, Mattismyrberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>559505</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7064062</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>129425339</v>
+      </c>
+      <c r="B28" t="n">
+        <v>82873</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Mattismyrberget, Mattismyrberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>559494</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7064095</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>129427281</v>
+      </c>
+      <c r="B29" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Mattismyrberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>559444</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7064122</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>129427275</v>
+      </c>
+      <c r="B30" t="n">
+        <v>91560</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Mattismyrberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>559455</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7064085</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>129424796</v>
+      </c>
+      <c r="B31" t="n">
+        <v>56301</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>206004</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Skogshare</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Lepus timidus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Mattismyrberget, Mattismyrberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>559439</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7064125</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>129424669</v>
+      </c>
+      <c r="B32" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Mattismyrberget, Mattismyrberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>559441</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7064183</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>129424832</v>
+      </c>
+      <c r="B33" t="n">
+        <v>80146</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Mattismyrberget, Mattismyrberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>559430</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7064092</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>14:16</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>14:16</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>På björk</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>129427252</v>
+      </c>
+      <c r="B34" t="n">
+        <v>83012</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>1467</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Rödbrun blekspik</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Sclerophora coniophaea</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Mattismyrberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>559475</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7064101</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>129425714</v>
+      </c>
+      <c r="B35" t="n">
+        <v>80146</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Mattismyrberget, Mattismyrberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>559500</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7064046</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>15:12</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>15:12</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>129424688</v>
+      </c>
+      <c r="B36" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Mattismyrberget, Mattismyrberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>559466</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7064165</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>129427276</v>
+      </c>
+      <c r="B37" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Mattismyrberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>559572</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7064054</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>129427248</v>
+      </c>
+      <c r="B38" t="n">
+        <v>91491</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>112</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Stjärntagging</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Asterodon ferruginosus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Pat.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Mattismyrberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>559581</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7064041</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>129427278</v>
+      </c>
+      <c r="B39" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Mattismyrberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>559539</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7064049</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 29563-2025 artfynd.xlsx
+++ b/artfynd/A 29563-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129402177</v>
       </c>
       <c r="B2" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>129411006</v>
       </c>
       <c r="B3" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>129402269</v>
       </c>
       <c r="B4" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>129410999</v>
       </c>
       <c r="B6" t="n">
-        <v>82990</v>
+        <v>82994</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1190,45 +1190,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129410985</v>
+        <v>129401658</v>
       </c>
       <c r="B7" t="n">
-        <v>97577</v>
+        <v>79043</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>559661</v>
+        <v>559658</v>
       </c>
       <c r="R7" t="n">
-        <v>7063971</v>
+        <v>7063991</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1258,9 +1258,19 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1275,12 +1285,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1290,7 +1300,7 @@
         <v>129402383</v>
       </c>
       <c r="B8" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1403,45 +1413,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129401658</v>
+        <v>129410985</v>
       </c>
       <c r="B9" t="n">
-        <v>79041</v>
+        <v>97581</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>559658</v>
+        <v>559661</v>
       </c>
       <c r="R9" t="n">
-        <v>7063991</v>
+        <v>7063971</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1471,19 +1481,9 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>11:59</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>11:59</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1498,12 +1498,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1513,7 +1513,7 @@
         <v>129410986</v>
       </c>
       <c r="B10" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>129411009</v>
       </c>
       <c r="B11" t="n">
-        <v>80181</v>
+        <v>80183</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>129410992</v>
       </c>
       <c r="B12" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         <v>129425378</v>
       </c>
       <c r="B13" t="n">
-        <v>91993</v>
+        <v>91996</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
         <v>129425867</v>
       </c>
       <c r="B14" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2034,41 +2034,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129425271</v>
+        <v>129427236</v>
       </c>
       <c r="B15" t="n">
-        <v>91560</v>
+        <v>91507</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Mattismyrberget, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>559486</v>
+        <v>559485</v>
       </c>
       <c r="R15" t="n">
-        <v>7064108</v>
+        <v>7064097</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2098,19 +2102,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>14:44</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>14:44</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2125,57 +2119,53 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129427236</v>
+        <v>129425271</v>
       </c>
       <c r="B16" t="n">
-        <v>91504</v>
+        <v>91563</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Mattismyrberget, Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>559485</v>
+        <v>559486</v>
       </c>
       <c r="R16" t="n">
-        <v>7064097</v>
+        <v>7064108</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2205,9 +2195,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>14:44</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2222,12 +2222,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2237,7 +2237,7 @@
         <v>129425134</v>
       </c>
       <c r="B17" t="n">
-        <v>82873</v>
+        <v>82877</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2341,32 +2341,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129427262</v>
+        <v>129427253</v>
       </c>
       <c r="B18" t="n">
-        <v>80146</v>
+        <v>91996</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2376,10 +2376,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>559585</v>
+        <v>559571</v>
       </c>
       <c r="R18" t="n">
-        <v>7064050</v>
+        <v>7064007</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2438,32 +2438,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129427253</v>
+        <v>129427262</v>
       </c>
       <c r="B19" t="n">
-        <v>91993</v>
+        <v>80148</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2473,10 +2473,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>559571</v>
+        <v>559585</v>
       </c>
       <c r="R19" t="n">
-        <v>7064007</v>
+        <v>7064050</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2538,7 +2538,7 @@
         <v>129427230</v>
       </c>
       <c r="B20" t="n">
-        <v>83007</v>
+        <v>83011</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2635,7 +2635,7 @@
         <v>129425894</v>
       </c>
       <c r="B21" t="n">
-        <v>82873</v>
+        <v>82877</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2742,7 +2742,7 @@
         <v>129427255</v>
       </c>
       <c r="B22" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2948,10 +2948,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129427280</v>
+        <v>129427251</v>
       </c>
       <c r="B24" t="n">
-        <v>79041</v>
+        <v>80149</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2959,21 +2959,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2983,10 +2983,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>559416</v>
+        <v>559590</v>
       </c>
       <c r="R24" t="n">
-        <v>7064119</v>
+        <v>7064053</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3045,10 +3045,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129427251</v>
+        <v>129427280</v>
       </c>
       <c r="B25" t="n">
-        <v>80147</v>
+        <v>79043</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3056,21 +3056,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3080,10 +3080,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>559590</v>
+        <v>559416</v>
       </c>
       <c r="R25" t="n">
-        <v>7064053</v>
+        <v>7064119</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3145,7 +3145,7 @@
         <v>129427261</v>
       </c>
       <c r="B26" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3239,10 +3239,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129425698</v>
+        <v>129425339</v>
       </c>
       <c r="B27" t="n">
-        <v>57727</v>
+        <v>82877</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3250,39 +3250,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Mattismyrberget, Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>559505</v>
+        <v>559494</v>
       </c>
       <c r="R27" t="n">
-        <v>7064062</v>
+        <v>7064095</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3314,7 +3309,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3324,12 +3319,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:10</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3356,10 +3346,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129425339</v>
+        <v>129425698</v>
       </c>
       <c r="B28" t="n">
-        <v>82873</v>
+        <v>57727</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3367,34 +3357,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Mattismyrberget, Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>559494</v>
+        <v>559505</v>
       </c>
       <c r="R28" t="n">
-        <v>7064095</v>
+        <v>7064062</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3426,7 +3421,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3436,7 +3431,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3466,7 +3466,7 @@
         <v>129427281</v>
       </c>
       <c r="B29" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3563,7 +3563,7 @@
         <v>129427275</v>
       </c>
       <c r="B30" t="n">
-        <v>91560</v>
+        <v>91563</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3768,7 +3768,7 @@
         <v>129424669</v>
       </c>
       <c r="B32" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3875,7 +3875,7 @@
         <v>129424832</v>
       </c>
       <c r="B33" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3987,7 +3987,7 @@
         <v>129427252</v>
       </c>
       <c r="B34" t="n">
-        <v>83012</v>
+        <v>83016</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4084,7 +4084,7 @@
         <v>129425714</v>
       </c>
       <c r="B35" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4188,10 +4188,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129424688</v>
+        <v>129427248</v>
       </c>
       <c r="B36" t="n">
-        <v>57727</v>
+        <v>91494</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4199,39 +4199,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>112</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Mattismyrberget, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>559466</v>
+        <v>559581</v>
       </c>
       <c r="R36" t="n">
-        <v>7064165</v>
+        <v>7064041</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4261,24 +4256,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>14:03</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>14:03</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4293,12 +4273,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -4308,7 +4288,7 @@
         <v>129427276</v>
       </c>
       <c r="B37" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4402,10 +4382,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129427248</v>
+        <v>129427278</v>
       </c>
       <c r="B38" t="n">
-        <v>91491</v>
+        <v>79043</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4413,21 +4393,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>112</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4437,10 +4417,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>559581</v>
+        <v>559539</v>
       </c>
       <c r="R38" t="n">
-        <v>7064041</v>
+        <v>7064049</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4499,10 +4479,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129427278</v>
+        <v>129424688</v>
       </c>
       <c r="B39" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4510,34 +4490,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Mattismyrberget, Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>559539</v>
+        <v>559466</v>
       </c>
       <c r="R39" t="n">
-        <v>7064049</v>
+        <v>7064165</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4567,9 +4552,24 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4584,12 +4584,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>

--- a/artfynd/A 29563-2025 artfynd.xlsx
+++ b/artfynd/A 29563-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129402177</v>
       </c>
       <c r="B2" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>129411006</v>
       </c>
       <c r="B3" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>129402269</v>
       </c>
       <c r="B4" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>129410999</v>
       </c>
       <c r="B6" t="n">
-        <v>82994</v>
+        <v>82995</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>129401658</v>
       </c>
       <c r="B7" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1297,54 +1297,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129402383</v>
+        <v>129410985</v>
       </c>
       <c r="B8" t="n">
-        <v>98710</v>
+        <v>97583</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>559592</v>
+        <v>559661</v>
       </c>
       <c r="R8" t="n">
-        <v>7064059</v>
+        <v>7063971</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1374,19 +1365,9 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>12:27</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>12:27</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1401,57 +1382,66 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129410985</v>
+        <v>129402383</v>
       </c>
       <c r="B9" t="n">
-        <v>97581</v>
+        <v>98712</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>559661</v>
+        <v>559592</v>
       </c>
       <c r="R9" t="n">
-        <v>7063971</v>
+        <v>7064059</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1481,9 +1471,19 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>12:27</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1498,12 +1498,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1513,7 +1513,7 @@
         <v>129410986</v>
       </c>
       <c r="B10" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>129411009</v>
       </c>
       <c r="B11" t="n">
-        <v>80183</v>
+        <v>80184</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>129410992</v>
       </c>
       <c r="B12" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         <v>129425378</v>
       </c>
       <c r="B13" t="n">
-        <v>91996</v>
+        <v>91998</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
         <v>129425867</v>
       </c>
       <c r="B14" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2034,45 +2034,41 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129427236</v>
+        <v>129425271</v>
       </c>
       <c r="B15" t="n">
-        <v>91507</v>
+        <v>91565</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Mattismyrberget, Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>559485</v>
+        <v>559486</v>
       </c>
       <c r="R15" t="n">
-        <v>7064097</v>
+        <v>7064108</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2102,9 +2098,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>14:44</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2119,53 +2125,57 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129425271</v>
+        <v>129427236</v>
       </c>
       <c r="B16" t="n">
-        <v>91563</v>
+        <v>91509</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Mattismyrberget, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>559486</v>
+        <v>559485</v>
       </c>
       <c r="R16" t="n">
-        <v>7064108</v>
+        <v>7064097</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2195,19 +2205,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>14:44</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>14:44</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2222,12 +2222,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2237,7 +2237,7 @@
         <v>129425134</v>
       </c>
       <c r="B17" t="n">
-        <v>82877</v>
+        <v>82878</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2341,32 +2341,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129427253</v>
+        <v>129427262</v>
       </c>
       <c r="B18" t="n">
-        <v>91996</v>
+        <v>80149</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2376,10 +2376,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>559571</v>
+        <v>559585</v>
       </c>
       <c r="R18" t="n">
-        <v>7064007</v>
+        <v>7064050</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2438,32 +2438,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129427262</v>
+        <v>129427253</v>
       </c>
       <c r="B19" t="n">
-        <v>80148</v>
+        <v>91998</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2473,10 +2473,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>559585</v>
+        <v>559571</v>
       </c>
       <c r="R19" t="n">
-        <v>7064050</v>
+        <v>7064007</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2538,7 +2538,7 @@
         <v>129427230</v>
       </c>
       <c r="B20" t="n">
-        <v>83011</v>
+        <v>83012</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2635,7 +2635,7 @@
         <v>129425894</v>
       </c>
       <c r="B21" t="n">
-        <v>82877</v>
+        <v>82878</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2742,7 +2742,7 @@
         <v>129427255</v>
       </c>
       <c r="B22" t="n">
-        <v>91841</v>
+        <v>91843</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2951,7 +2951,7 @@
         <v>129427251</v>
       </c>
       <c r="B24" t="n">
-        <v>80149</v>
+        <v>80150</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3048,7 +3048,7 @@
         <v>129427280</v>
       </c>
       <c r="B25" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3145,7 +3145,7 @@
         <v>129427261</v>
       </c>
       <c r="B26" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
         <v>129425339</v>
       </c>
       <c r="B27" t="n">
-        <v>82877</v>
+        <v>82878</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3466,7 +3466,7 @@
         <v>129427281</v>
       </c>
       <c r="B29" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3563,7 +3563,7 @@
         <v>129427275</v>
       </c>
       <c r="B30" t="n">
-        <v>91563</v>
+        <v>91565</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3765,10 +3765,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129424669</v>
+        <v>129424832</v>
       </c>
       <c r="B32" t="n">
-        <v>79043</v>
+        <v>80149</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3776,21 +3776,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3800,10 +3800,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>559441</v>
+        <v>559430</v>
       </c>
       <c r="R32" t="n">
-        <v>7064183</v>
+        <v>7064092</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3835,7 +3835,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3845,7 +3845,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:16</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3872,10 +3877,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129424832</v>
+        <v>129424669</v>
       </c>
       <c r="B33" t="n">
-        <v>80148</v>
+        <v>79044</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3883,21 +3888,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3907,10 +3912,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>559430</v>
+        <v>559441</v>
       </c>
       <c r="R33" t="n">
-        <v>7064092</v>
+        <v>7064183</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3942,7 +3947,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -3952,12 +3957,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:16</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>På björk</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3987,7 +3987,7 @@
         <v>129427252</v>
       </c>
       <c r="B34" t="n">
-        <v>83016</v>
+        <v>83017</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4084,7 +4084,7 @@
         <v>129425714</v>
       </c>
       <c r="B35" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4188,10 +4188,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129427248</v>
+        <v>129427276</v>
       </c>
       <c r="B36" t="n">
-        <v>91494</v>
+        <v>79044</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4199,21 +4199,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>112</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4223,10 +4223,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>559581</v>
+        <v>559572</v>
       </c>
       <c r="R36" t="n">
-        <v>7064041</v>
+        <v>7064054</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4285,10 +4285,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129427276</v>
+        <v>129427278</v>
       </c>
       <c r="B37" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4320,10 +4320,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>559572</v>
+        <v>559539</v>
       </c>
       <c r="R37" t="n">
-        <v>7064054</v>
+        <v>7064049</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4382,10 +4382,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129427278</v>
+        <v>129424688</v>
       </c>
       <c r="B38" t="n">
-        <v>79043</v>
+        <v>57727</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4393,34 +4393,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Mattismyrberget, Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>559539</v>
+        <v>559466</v>
       </c>
       <c r="R38" t="n">
-        <v>7064049</v>
+        <v>7064165</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4450,9 +4455,24 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4467,22 +4487,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129424688</v>
+        <v>129427248</v>
       </c>
       <c r="B39" t="n">
-        <v>57727</v>
+        <v>91496</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4490,39 +4510,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>112</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Mattismyrberget, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>559466</v>
+        <v>559581</v>
       </c>
       <c r="R39" t="n">
-        <v>7064165</v>
+        <v>7064041</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4552,24 +4567,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>14:03</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>14:03</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4584,12 +4584,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>

--- a/artfynd/A 29563-2025 artfynd.xlsx
+++ b/artfynd/A 29563-2025 artfynd.xlsx
@@ -1300,7 +1300,7 @@
         <v>129410985</v>
       </c>
       <c r="B8" t="n">
-        <v>97583</v>
+        <v>97587</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>129402383</v>
       </c>
       <c r="B9" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         <v>129425378</v>
       </c>
       <c r="B13" t="n">
-        <v>91998</v>
+        <v>92002</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1927,45 +1927,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129425867</v>
+        <v>129427236</v>
       </c>
       <c r="B14" t="n">
-        <v>79044</v>
+        <v>91513</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Mattismyrberget, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>559534</v>
+        <v>559485</v>
       </c>
       <c r="R14" t="n">
-        <v>7064000</v>
+        <v>7064097</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1995,19 +1995,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>15:23</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>15:23</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2022,12 +2012,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2037,7 +2027,7 @@
         <v>129425271</v>
       </c>
       <c r="B15" t="n">
-        <v>91565</v>
+        <v>91569</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2137,45 +2127,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129427236</v>
+        <v>129425867</v>
       </c>
       <c r="B16" t="n">
-        <v>91509</v>
+        <v>79044</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Mattismyrberget, Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>559485</v>
+        <v>559534</v>
       </c>
       <c r="R16" t="n">
-        <v>7064097</v>
+        <v>7064000</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2205,9 +2195,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>15:23</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2222,12 +2222,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2341,32 +2341,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129427262</v>
+        <v>129427253</v>
       </c>
       <c r="B18" t="n">
-        <v>80149</v>
+        <v>92002</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2376,10 +2376,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>559585</v>
+        <v>559571</v>
       </c>
       <c r="R18" t="n">
-        <v>7064050</v>
+        <v>7064007</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2438,32 +2438,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129427253</v>
+        <v>129427262</v>
       </c>
       <c r="B19" t="n">
-        <v>91998</v>
+        <v>80149</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2473,10 +2473,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>559571</v>
+        <v>559585</v>
       </c>
       <c r="R19" t="n">
-        <v>7064007</v>
+        <v>7064050</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2739,10 +2739,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129427255</v>
+        <v>129425250</v>
       </c>
       <c r="B22" t="n">
-        <v>91843</v>
+        <v>57724</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2750,34 +2750,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Mattismyrberget, Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>559572</v>
+        <v>559469</v>
       </c>
       <c r="R22" t="n">
-        <v>7064006</v>
+        <v>7064105</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2807,9 +2812,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2824,22 +2839,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129425250</v>
+        <v>129427255</v>
       </c>
       <c r="B23" t="n">
-        <v>57724</v>
+        <v>91847</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2847,39 +2862,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Mattismyrberget, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>559469</v>
+        <v>559572</v>
       </c>
       <c r="R23" t="n">
-        <v>7064105</v>
+        <v>7064006</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2909,19 +2919,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>14:40</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>14:40</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2936,22 +2936,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129427251</v>
+        <v>129427280</v>
       </c>
       <c r="B24" t="n">
-        <v>80150</v>
+        <v>79044</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2959,21 +2959,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2983,10 +2983,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>559590</v>
+        <v>559416</v>
       </c>
       <c r="R24" t="n">
-        <v>7064053</v>
+        <v>7064119</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3045,10 +3045,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129427280</v>
+        <v>129427251</v>
       </c>
       <c r="B25" t="n">
-        <v>79044</v>
+        <v>80150</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3056,21 +3056,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3080,10 +3080,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>559416</v>
+        <v>559590</v>
       </c>
       <c r="R25" t="n">
-        <v>7064119</v>
+        <v>7064053</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3563,7 +3563,7 @@
         <v>129427275</v>
       </c>
       <c r="B30" t="n">
-        <v>91565</v>
+        <v>91569</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4188,10 +4188,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129427276</v>
+        <v>129424688</v>
       </c>
       <c r="B36" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4199,34 +4199,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Mattismyrberget, Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>559572</v>
+        <v>559466</v>
       </c>
       <c r="R36" t="n">
-        <v>7064054</v>
+        <v>7064165</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4256,9 +4261,24 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4273,19 +4293,19 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129427278</v>
+        <v>129427276</v>
       </c>
       <c r="B37" t="n">
         <v>79044</v>
@@ -4320,10 +4340,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>559539</v>
+        <v>559572</v>
       </c>
       <c r="R37" t="n">
-        <v>7064049</v>
+        <v>7064054</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4382,10 +4402,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129424688</v>
+        <v>129427278</v>
       </c>
       <c r="B38" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4393,39 +4413,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Mattismyrberget, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>559466</v>
+        <v>559539</v>
       </c>
       <c r="R38" t="n">
-        <v>7064165</v>
+        <v>7064049</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4455,24 +4470,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>14:03</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>14:03</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4487,12 +4487,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -4502,7 +4502,7 @@
         <v>129427248</v>
       </c>
       <c r="B39" t="n">
-        <v>91496</v>
+        <v>91500</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 29563-2025 artfynd.xlsx
+++ b/artfynd/A 29563-2025 artfynd.xlsx
@@ -1300,7 +1300,7 @@
         <v>129410985</v>
       </c>
       <c r="B8" t="n">
-        <v>97587</v>
+        <v>97595</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>129402383</v>
       </c>
       <c r="B9" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         <v>129425378</v>
       </c>
       <c r="B13" t="n">
-        <v>92002</v>
+        <v>92003</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1927,45 +1927,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129427236</v>
+        <v>129425867</v>
       </c>
       <c r="B14" t="n">
-        <v>91513</v>
+        <v>79044</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Mattismyrberget, Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>559485</v>
+        <v>559534</v>
       </c>
       <c r="R14" t="n">
-        <v>7064097</v>
+        <v>7064000</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1995,9 +1995,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>15:23</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2012,53 +2022,57 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129425271</v>
+        <v>129427236</v>
       </c>
       <c r="B15" t="n">
-        <v>91569</v>
+        <v>91514</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Mattismyrberget, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>559486</v>
+        <v>559485</v>
       </c>
       <c r="R15" t="n">
-        <v>7064108</v>
+        <v>7064097</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2088,19 +2102,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>14:44</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>14:44</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2115,22 +2119,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129425867</v>
+        <v>129425271</v>
       </c>
       <c r="B16" t="n">
-        <v>79044</v>
+        <v>91570</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2138,23 +2142,19 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2162,10 +2162,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>559534</v>
+        <v>559486</v>
       </c>
       <c r="R16" t="n">
-        <v>7064000</v>
+        <v>7064108</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2197,7 +2197,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2207,7 +2207,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2341,32 +2341,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129427253</v>
+        <v>129427230</v>
       </c>
       <c r="B18" t="n">
-        <v>92002</v>
+        <v>83012</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1209</v>
+        <v>6440</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2376,10 +2376,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>559571</v>
+        <v>559425</v>
       </c>
       <c r="R18" t="n">
-        <v>7064007</v>
+        <v>7064125</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2438,32 +2438,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129427262</v>
+        <v>129427253</v>
       </c>
       <c r="B19" t="n">
-        <v>80149</v>
+        <v>92003</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2473,10 +2473,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>559585</v>
+        <v>559571</v>
       </c>
       <c r="R19" t="n">
-        <v>7064050</v>
+        <v>7064007</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2535,10 +2535,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129427230</v>
+        <v>129427262</v>
       </c>
       <c r="B20" t="n">
-        <v>83012</v>
+        <v>80149</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2546,21 +2546,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2570,10 +2570,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>559425</v>
+        <v>559585</v>
       </c>
       <c r="R20" t="n">
-        <v>7064125</v>
+        <v>7064050</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2739,10 +2739,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129425250</v>
+        <v>129427255</v>
       </c>
       <c r="B22" t="n">
-        <v>57724</v>
+        <v>91848</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2750,39 +2750,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Mattismyrberget, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>559469</v>
+        <v>559572</v>
       </c>
       <c r="R22" t="n">
-        <v>7064105</v>
+        <v>7064006</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2812,19 +2807,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>14:40</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>14:40</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2839,22 +2824,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129427255</v>
+        <v>129425250</v>
       </c>
       <c r="B23" t="n">
-        <v>91847</v>
+        <v>57724</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2862,34 +2847,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Mattismyrberget, Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>559572</v>
+        <v>559469</v>
       </c>
       <c r="R23" t="n">
-        <v>7064006</v>
+        <v>7064105</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2919,9 +2909,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2936,22 +2936,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129427280</v>
+        <v>129427251</v>
       </c>
       <c r="B24" t="n">
-        <v>79044</v>
+        <v>80150</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2959,21 +2959,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2983,10 +2983,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>559416</v>
+        <v>559590</v>
       </c>
       <c r="R24" t="n">
-        <v>7064119</v>
+        <v>7064053</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3045,10 +3045,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129427251</v>
+        <v>129427280</v>
       </c>
       <c r="B25" t="n">
-        <v>80150</v>
+        <v>79044</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3056,21 +3056,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3080,10 +3080,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>559590</v>
+        <v>559416</v>
       </c>
       <c r="R25" t="n">
-        <v>7064053</v>
+        <v>7064119</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3563,7 +3563,7 @@
         <v>129427275</v>
       </c>
       <c r="B30" t="n">
-        <v>91569</v>
+        <v>91570</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3765,10 +3765,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129424832</v>
+        <v>129424669</v>
       </c>
       <c r="B32" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3776,21 +3776,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3800,10 +3800,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>559430</v>
+        <v>559441</v>
       </c>
       <c r="R32" t="n">
-        <v>7064092</v>
+        <v>7064183</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3835,7 +3835,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3845,12 +3845,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:16</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>På björk</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3877,10 +3872,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129424669</v>
+        <v>129424832</v>
       </c>
       <c r="B33" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3888,21 +3883,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3912,10 +3907,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>559441</v>
+        <v>559430</v>
       </c>
       <c r="R33" t="n">
-        <v>7064183</v>
+        <v>7064092</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3947,7 +3942,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -3957,7 +3952,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:16</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4188,10 +4188,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129424688</v>
+        <v>129427276</v>
       </c>
       <c r="B36" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4199,39 +4199,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Mattismyrberget, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>559466</v>
+        <v>559572</v>
       </c>
       <c r="R36" t="n">
-        <v>7064165</v>
+        <v>7064054</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4261,24 +4256,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>14:03</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>14:03</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4293,22 +4273,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129427276</v>
+        <v>129427248</v>
       </c>
       <c r="B37" t="n">
-        <v>79044</v>
+        <v>91501</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4316,21 +4296,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>112</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4340,10 +4320,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>559572</v>
+        <v>559581</v>
       </c>
       <c r="R37" t="n">
-        <v>7064054</v>
+        <v>7064041</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4499,10 +4479,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129427248</v>
+        <v>129424688</v>
       </c>
       <c r="B39" t="n">
-        <v>91500</v>
+        <v>57727</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4510,34 +4490,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>112</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Mattismyrberget, Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>559581</v>
+        <v>559466</v>
       </c>
       <c r="R39" t="n">
-        <v>7064041</v>
+        <v>7064165</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4567,9 +4552,24 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4584,12 +4584,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>

--- a/artfynd/A 29563-2025 artfynd.xlsx
+++ b/artfynd/A 29563-2025 artfynd.xlsx
@@ -1297,45 +1297,54 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129410985</v>
+        <v>129402383</v>
       </c>
       <c r="B8" t="n">
-        <v>97595</v>
+        <v>98724</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>559661</v>
+        <v>559592</v>
       </c>
       <c r="R8" t="n">
-        <v>7063971</v>
+        <v>7064059</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1365,9 +1374,19 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>12:27</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1382,66 +1401,57 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129402383</v>
+        <v>129410985</v>
       </c>
       <c r="B9" t="n">
-        <v>98724</v>
+        <v>97595</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>559592</v>
+        <v>559661</v>
       </c>
       <c r="R9" t="n">
-        <v>7064059</v>
+        <v>7063971</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1471,19 +1481,9 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>12:27</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>12:27</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1498,12 +1498,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1927,45 +1927,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129425867</v>
+        <v>129427236</v>
       </c>
       <c r="B14" t="n">
-        <v>79044</v>
+        <v>91514</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Mattismyrberget, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>559534</v>
+        <v>559485</v>
       </c>
       <c r="R14" t="n">
-        <v>7064000</v>
+        <v>7064097</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1995,19 +1995,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>15:23</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>15:23</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2022,57 +2012,57 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129427236</v>
+        <v>129425867</v>
       </c>
       <c r="B15" t="n">
-        <v>91514</v>
+        <v>79044</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Mattismyrberget, Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>559485</v>
+        <v>559534</v>
       </c>
       <c r="R15" t="n">
-        <v>7064097</v>
+        <v>7064000</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2102,9 +2092,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>15:23</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2119,12 +2119,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2341,10 +2341,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129427230</v>
+        <v>129427262</v>
       </c>
       <c r="B18" t="n">
-        <v>83012</v>
+        <v>80149</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2352,21 +2352,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2376,10 +2376,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>559425</v>
+        <v>559585</v>
       </c>
       <c r="R18" t="n">
-        <v>7064125</v>
+        <v>7064050</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2438,32 +2438,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129427253</v>
+        <v>129427230</v>
       </c>
       <c r="B19" t="n">
-        <v>92003</v>
+        <v>83012</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1209</v>
+        <v>6440</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2473,10 +2473,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>559571</v>
+        <v>559425</v>
       </c>
       <c r="R19" t="n">
-        <v>7064007</v>
+        <v>7064125</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2535,32 +2535,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129427262</v>
+        <v>129427253</v>
       </c>
       <c r="B20" t="n">
-        <v>80149</v>
+        <v>92003</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2570,10 +2570,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>559585</v>
+        <v>559571</v>
       </c>
       <c r="R20" t="n">
-        <v>7064050</v>
+        <v>7064007</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2948,10 +2948,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129427251</v>
+        <v>129427280</v>
       </c>
       <c r="B24" t="n">
-        <v>80150</v>
+        <v>79044</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2959,21 +2959,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2983,10 +2983,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>559590</v>
+        <v>559416</v>
       </c>
       <c r="R24" t="n">
-        <v>7064053</v>
+        <v>7064119</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3045,10 +3045,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129427280</v>
+        <v>129427251</v>
       </c>
       <c r="B25" t="n">
-        <v>79044</v>
+        <v>80150</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3056,21 +3056,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3080,10 +3080,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>559416</v>
+        <v>559590</v>
       </c>
       <c r="R25" t="n">
-        <v>7064119</v>
+        <v>7064053</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -4285,10 +4285,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129427248</v>
+        <v>129427278</v>
       </c>
       <c r="B37" t="n">
-        <v>91501</v>
+        <v>79044</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4296,21 +4296,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>112</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4320,10 +4320,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>559581</v>
+        <v>559539</v>
       </c>
       <c r="R37" t="n">
-        <v>7064041</v>
+        <v>7064049</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4382,10 +4382,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129427278</v>
+        <v>129427248</v>
       </c>
       <c r="B38" t="n">
-        <v>79044</v>
+        <v>91501</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4393,21 +4393,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>112</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4417,10 +4417,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>559539</v>
+        <v>559581</v>
       </c>
       <c r="R38" t="n">
-        <v>7064049</v>
+        <v>7064041</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>

--- a/artfynd/A 29563-2025 artfynd.xlsx
+++ b/artfynd/A 29563-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY39"/>
+  <dimension ref="A1:AY40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2739,10 +2739,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129427255</v>
+        <v>129425250</v>
       </c>
       <c r="B22" t="n">
-        <v>91848</v>
+        <v>57724</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2750,34 +2750,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Mattismyrberget, Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>559572</v>
+        <v>559469</v>
       </c>
       <c r="R22" t="n">
-        <v>7064006</v>
+        <v>7064105</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2807,9 +2812,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2824,22 +2839,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129425250</v>
+        <v>129427255</v>
       </c>
       <c r="B23" t="n">
-        <v>57724</v>
+        <v>91848</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2847,39 +2862,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Mattismyrberget, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>559469</v>
+        <v>559572</v>
       </c>
       <c r="R23" t="n">
-        <v>7064105</v>
+        <v>7064006</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2909,19 +2919,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>14:40</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>14:40</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2936,22 +2936,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129427280</v>
+        <v>129427251</v>
       </c>
       <c r="B24" t="n">
-        <v>79044</v>
+        <v>80150</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2959,21 +2959,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2983,10 +2983,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>559416</v>
+        <v>559590</v>
       </c>
       <c r="R24" t="n">
-        <v>7064119</v>
+        <v>7064053</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3045,10 +3045,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129427251</v>
+        <v>129427280</v>
       </c>
       <c r="B25" t="n">
-        <v>80150</v>
+        <v>79044</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3056,21 +3056,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3080,10 +3080,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>559590</v>
+        <v>559416</v>
       </c>
       <c r="R25" t="n">
-        <v>7064053</v>
+        <v>7064119</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -4382,10 +4382,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129427248</v>
+        <v>129424688</v>
       </c>
       <c r="B38" t="n">
-        <v>91501</v>
+        <v>57727</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4393,34 +4393,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>112</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Mattismyrberget, Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>559581</v>
+        <v>559466</v>
       </c>
       <c r="R38" t="n">
-        <v>7064041</v>
+        <v>7064165</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4450,9 +4455,24 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4467,22 +4487,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129424688</v>
+        <v>129427248</v>
       </c>
       <c r="B39" t="n">
-        <v>57727</v>
+        <v>91501</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4490,39 +4510,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>112</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Mattismyrberget, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>559466</v>
+        <v>559581</v>
       </c>
       <c r="R39" t="n">
-        <v>7064165</v>
+        <v>7064041</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4552,24 +4567,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>14:03</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>14:03</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4584,15 +4584,131 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>129546496</v>
+      </c>
+      <c r="B40" t="n">
+        <v>98724</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Spångmyran, Spångmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>559660</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7063975</v>
+      </c>
+      <c r="S40" t="n">
+        <v>4</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>09:25</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>09:25</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Peter von Troil</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Peter von Troil</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 29563-2025 artfynd.xlsx
+++ b/artfynd/A 29563-2025 artfynd.xlsx
@@ -1297,54 +1297,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129402383</v>
+        <v>129410985</v>
       </c>
       <c r="B8" t="n">
-        <v>98724</v>
+        <v>97598</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>559592</v>
+        <v>559661</v>
       </c>
       <c r="R8" t="n">
-        <v>7064059</v>
+        <v>7063971</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1374,19 +1365,9 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>12:27</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>12:27</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1401,57 +1382,66 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129410985</v>
+        <v>129402383</v>
       </c>
       <c r="B9" t="n">
-        <v>97595</v>
+        <v>98727</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>559661</v>
+        <v>559592</v>
       </c>
       <c r="R9" t="n">
-        <v>7063971</v>
+        <v>7064059</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1481,9 +1471,19 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>12:27</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1498,12 +1498,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1823,7 +1823,7 @@
         <v>129425378</v>
       </c>
       <c r="B13" t="n">
-        <v>92003</v>
+        <v>92006</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1927,45 +1927,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129427236</v>
+        <v>129425867</v>
       </c>
       <c r="B14" t="n">
-        <v>91514</v>
+        <v>79044</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Mattismyrberget, Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>559485</v>
+        <v>559534</v>
       </c>
       <c r="R14" t="n">
-        <v>7064097</v>
+        <v>7064000</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1995,9 +1995,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>15:23</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2012,57 +2022,57 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129425867</v>
+        <v>129427236</v>
       </c>
       <c r="B15" t="n">
-        <v>79044</v>
+        <v>91517</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Mattismyrberget, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>559534</v>
+        <v>559485</v>
       </c>
       <c r="R15" t="n">
-        <v>7064000</v>
+        <v>7064097</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2092,19 +2102,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>15:23</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>15:23</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2119,12 +2119,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2134,7 +2134,7 @@
         <v>129425271</v>
       </c>
       <c r="B16" t="n">
-        <v>91570</v>
+        <v>91573</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>129427253</v>
       </c>
       <c r="B20" t="n">
-        <v>92003</v>
+        <v>92006</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2739,10 +2739,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129425250</v>
+        <v>129427255</v>
       </c>
       <c r="B22" t="n">
-        <v>57724</v>
+        <v>91851</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2750,39 +2750,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Mattismyrberget, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>559469</v>
+        <v>559572</v>
       </c>
       <c r="R22" t="n">
-        <v>7064105</v>
+        <v>7064006</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2812,19 +2807,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>14:40</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>14:40</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2839,22 +2824,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129427255</v>
+        <v>129425250</v>
       </c>
       <c r="B23" t="n">
-        <v>91848</v>
+        <v>57724</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2862,34 +2847,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Mattismyrberget, Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>559572</v>
+        <v>559469</v>
       </c>
       <c r="R23" t="n">
-        <v>7064006</v>
+        <v>7064105</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2919,9 +2909,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2936,12 +2936,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -3563,7 +3563,7 @@
         <v>129427275</v>
       </c>
       <c r="B30" t="n">
-        <v>91570</v>
+        <v>91573</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4188,10 +4188,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129427276</v>
+        <v>129427248</v>
       </c>
       <c r="B36" t="n">
-        <v>79044</v>
+        <v>91504</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4199,21 +4199,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>112</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4223,10 +4223,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>559572</v>
+        <v>559581</v>
       </c>
       <c r="R36" t="n">
-        <v>7064054</v>
+        <v>7064041</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4285,7 +4285,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129427278</v>
+        <v>129427276</v>
       </c>
       <c r="B37" t="n">
         <v>79044</v>
@@ -4320,10 +4320,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>559539</v>
+        <v>559572</v>
       </c>
       <c r="R37" t="n">
-        <v>7064049</v>
+        <v>7064054</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4382,10 +4382,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129424688</v>
+        <v>129427278</v>
       </c>
       <c r="B38" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4393,39 +4393,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Mattismyrberget, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>559466</v>
+        <v>559539</v>
       </c>
       <c r="R38" t="n">
-        <v>7064165</v>
+        <v>7064049</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4455,24 +4450,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>14:03</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>14:03</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4487,22 +4467,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129427248</v>
+        <v>129424688</v>
       </c>
       <c r="B39" t="n">
-        <v>91501</v>
+        <v>57727</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4510,34 +4490,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>112</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Mattismyrberget, Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>559581</v>
+        <v>559466</v>
       </c>
       <c r="R39" t="n">
-        <v>7064041</v>
+        <v>7064165</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4567,9 +4552,24 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4584,12 +4584,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -4599,7 +4599,7 @@
         <v>129546496</v>
       </c>
       <c r="B40" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 29563-2025 artfynd.xlsx
+++ b/artfynd/A 29563-2025 artfynd.xlsx
@@ -1190,45 +1190,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129401658</v>
+        <v>129410985</v>
       </c>
       <c r="B7" t="n">
-        <v>79044</v>
+        <v>97598</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>559658</v>
+        <v>559661</v>
       </c>
       <c r="R7" t="n">
-        <v>7063991</v>
+        <v>7063971</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1258,19 +1258,9 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>11:59</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>11:59</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1285,57 +1275,57 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129410985</v>
+        <v>129401658</v>
       </c>
       <c r="B8" t="n">
-        <v>97598</v>
+        <v>79044</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>559661</v>
+        <v>559658</v>
       </c>
       <c r="R8" t="n">
-        <v>7063971</v>
+        <v>7063991</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1365,9 +1355,19 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1382,12 +1382,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1927,45 +1927,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129425867</v>
+        <v>129427236</v>
       </c>
       <c r="B14" t="n">
-        <v>79044</v>
+        <v>91517</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Mattismyrberget, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>559534</v>
+        <v>559485</v>
       </c>
       <c r="R14" t="n">
-        <v>7064000</v>
+        <v>7064097</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1995,19 +1995,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>15:23</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>15:23</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2022,57 +2012,53 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129427236</v>
+        <v>129425271</v>
       </c>
       <c r="B15" t="n">
-        <v>91517</v>
+        <v>91573</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Mattismyrberget, Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>559485</v>
+        <v>559486</v>
       </c>
       <c r="R15" t="n">
-        <v>7064097</v>
+        <v>7064108</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2102,9 +2088,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>14:44</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2119,22 +2115,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129425271</v>
+        <v>129425867</v>
       </c>
       <c r="B16" t="n">
-        <v>91573</v>
+        <v>79044</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2142,19 +2138,23 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2162,10 +2162,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>559486</v>
+        <v>559534</v>
       </c>
       <c r="R16" t="n">
-        <v>7064108</v>
+        <v>7064000</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2197,7 +2197,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2207,7 +2207,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2341,32 +2341,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129427262</v>
+        <v>129427253</v>
       </c>
       <c r="B18" t="n">
-        <v>80149</v>
+        <v>92006</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2376,10 +2376,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>559585</v>
+        <v>559571</v>
       </c>
       <c r="R18" t="n">
-        <v>7064050</v>
+        <v>7064007</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2438,10 +2438,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129427230</v>
+        <v>129427262</v>
       </c>
       <c r="B19" t="n">
-        <v>83012</v>
+        <v>80149</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2449,21 +2449,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2473,10 +2473,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>559425</v>
+        <v>559585</v>
       </c>
       <c r="R19" t="n">
-        <v>7064125</v>
+        <v>7064050</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2535,32 +2535,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129427253</v>
+        <v>129427230</v>
       </c>
       <c r="B20" t="n">
-        <v>92006</v>
+        <v>83012</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1209</v>
+        <v>6440</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2570,10 +2570,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>559571</v>
+        <v>559425</v>
       </c>
       <c r="R20" t="n">
-        <v>7064007</v>
+        <v>7064125</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -4188,10 +4188,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129427248</v>
+        <v>129427276</v>
       </c>
       <c r="B36" t="n">
-        <v>91504</v>
+        <v>79044</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4199,21 +4199,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>112</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4223,10 +4223,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>559581</v>
+        <v>559572</v>
       </c>
       <c r="R36" t="n">
-        <v>7064041</v>
+        <v>7064054</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4285,7 +4285,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129427276</v>
+        <v>129427278</v>
       </c>
       <c r="B37" t="n">
         <v>79044</v>
@@ -4320,10 +4320,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>559572</v>
+        <v>559539</v>
       </c>
       <c r="R37" t="n">
-        <v>7064054</v>
+        <v>7064049</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4382,10 +4382,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129427278</v>
+        <v>129424688</v>
       </c>
       <c r="B38" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4393,34 +4393,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Mattismyrberget, Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>559539</v>
+        <v>559466</v>
       </c>
       <c r="R38" t="n">
-        <v>7064049</v>
+        <v>7064165</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4450,9 +4455,24 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4467,22 +4487,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129424688</v>
+        <v>129427248</v>
       </c>
       <c r="B39" t="n">
-        <v>57727</v>
+        <v>91504</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4490,39 +4510,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>112</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Mattismyrberget, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>559466</v>
+        <v>559581</v>
       </c>
       <c r="R39" t="n">
-        <v>7064165</v>
+        <v>7064041</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4552,24 +4567,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>14:03</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>14:03</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4584,12 +4584,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>

--- a/artfynd/A 29563-2025 artfynd.xlsx
+++ b/artfynd/A 29563-2025 artfynd.xlsx
@@ -1190,45 +1190,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129410985</v>
+        <v>129401658</v>
       </c>
       <c r="B7" t="n">
-        <v>97598</v>
+        <v>79044</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>559661</v>
+        <v>559658</v>
       </c>
       <c r="R7" t="n">
-        <v>7063971</v>
+        <v>7063991</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1258,9 +1258,19 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1275,57 +1285,57 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129401658</v>
+        <v>129410985</v>
       </c>
       <c r="B8" t="n">
-        <v>79044</v>
+        <v>97598</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>559658</v>
+        <v>559661</v>
       </c>
       <c r="R8" t="n">
-        <v>7063991</v>
+        <v>7063971</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1355,19 +1365,9 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>11:59</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>11:59</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1382,12 +1382,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1927,45 +1927,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129427236</v>
+        <v>129425867</v>
       </c>
       <c r="B14" t="n">
-        <v>91517</v>
+        <v>79044</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Mattismyrberget, Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>559485</v>
+        <v>559534</v>
       </c>
       <c r="R14" t="n">
-        <v>7064097</v>
+        <v>7064000</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1995,9 +1995,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>15:23</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2012,53 +2022,57 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129425271</v>
+        <v>129427236</v>
       </c>
       <c r="B15" t="n">
-        <v>91573</v>
+        <v>91517</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Mattismyrberget, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>559486</v>
+        <v>559485</v>
       </c>
       <c r="R15" t="n">
-        <v>7064108</v>
+        <v>7064097</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2088,19 +2102,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>14:44</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>14:44</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2115,22 +2119,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129425867</v>
+        <v>129425271</v>
       </c>
       <c r="B16" t="n">
-        <v>79044</v>
+        <v>91573</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2138,23 +2142,19 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2162,10 +2162,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>559534</v>
+        <v>559486</v>
       </c>
       <c r="R16" t="n">
-        <v>7064000</v>
+        <v>7064108</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2197,7 +2197,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2207,7 +2207,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2341,32 +2341,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129427253</v>
+        <v>129427230</v>
       </c>
       <c r="B18" t="n">
-        <v>92006</v>
+        <v>83012</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1209</v>
+        <v>6440</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2376,10 +2376,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>559571</v>
+        <v>559425</v>
       </c>
       <c r="R18" t="n">
-        <v>7064007</v>
+        <v>7064125</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2438,32 +2438,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129427262</v>
+        <v>129427253</v>
       </c>
       <c r="B19" t="n">
-        <v>80149</v>
+        <v>92006</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2473,10 +2473,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>559585</v>
+        <v>559571</v>
       </c>
       <c r="R19" t="n">
-        <v>7064050</v>
+        <v>7064007</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2535,10 +2535,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129427230</v>
+        <v>129427262</v>
       </c>
       <c r="B20" t="n">
-        <v>83012</v>
+        <v>80149</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2546,21 +2546,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2570,10 +2570,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>559425</v>
+        <v>559585</v>
       </c>
       <c r="R20" t="n">
-        <v>7064125</v>
+        <v>7064050</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -4382,10 +4382,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129424688</v>
+        <v>129427248</v>
       </c>
       <c r="B38" t="n">
-        <v>57727</v>
+        <v>91504</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4393,39 +4393,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>112</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Mattismyrberget, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>559466</v>
+        <v>559581</v>
       </c>
       <c r="R38" t="n">
-        <v>7064165</v>
+        <v>7064041</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4455,24 +4450,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>14:03</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>14:03</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4487,22 +4467,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129427248</v>
+        <v>129424688</v>
       </c>
       <c r="B39" t="n">
-        <v>91504</v>
+        <v>57727</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4510,34 +4490,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>112</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Mattismyrberget, Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>559581</v>
+        <v>559466</v>
       </c>
       <c r="R39" t="n">
-        <v>7064041</v>
+        <v>7064165</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4567,9 +4552,24 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4584,12 +4584,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>

--- a/artfynd/A 29563-2025 artfynd.xlsx
+++ b/artfynd/A 29563-2025 artfynd.xlsx
@@ -1927,45 +1927,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129425867</v>
+        <v>129427236</v>
       </c>
       <c r="B14" t="n">
-        <v>79044</v>
+        <v>91517</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Mattismyrberget, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>559534</v>
+        <v>559485</v>
       </c>
       <c r="R14" t="n">
-        <v>7064000</v>
+        <v>7064097</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1995,19 +1995,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>15:23</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>15:23</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2022,57 +2012,57 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129427236</v>
+        <v>129425867</v>
       </c>
       <c r="B15" t="n">
-        <v>91517</v>
+        <v>79044</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Mattismyrberget, Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>559485</v>
+        <v>559534</v>
       </c>
       <c r="R15" t="n">
-        <v>7064097</v>
+        <v>7064000</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2102,9 +2092,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>15:23</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2119,12 +2119,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2341,10 +2341,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129427230</v>
+        <v>129427262</v>
       </c>
       <c r="B18" t="n">
-        <v>83012</v>
+        <v>80149</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2352,21 +2352,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2376,10 +2376,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>559425</v>
+        <v>559585</v>
       </c>
       <c r="R18" t="n">
-        <v>7064125</v>
+        <v>7064050</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2438,32 +2438,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129427253</v>
+        <v>129427230</v>
       </c>
       <c r="B19" t="n">
-        <v>92006</v>
+        <v>83012</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1209</v>
+        <v>6440</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2473,10 +2473,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>559571</v>
+        <v>559425</v>
       </c>
       <c r="R19" t="n">
-        <v>7064007</v>
+        <v>7064125</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2535,32 +2535,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129427262</v>
+        <v>129427253</v>
       </c>
       <c r="B20" t="n">
-        <v>80149</v>
+        <v>92006</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2570,10 +2570,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>559585</v>
+        <v>559571</v>
       </c>
       <c r="R20" t="n">
-        <v>7064050</v>
+        <v>7064007</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -4188,10 +4188,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129427276</v>
+        <v>129427248</v>
       </c>
       <c r="B36" t="n">
-        <v>79044</v>
+        <v>91504</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4199,21 +4199,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>112</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4223,10 +4223,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>559572</v>
+        <v>559581</v>
       </c>
       <c r="R36" t="n">
-        <v>7064054</v>
+        <v>7064041</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4285,7 +4285,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129427278</v>
+        <v>129427276</v>
       </c>
       <c r="B37" t="n">
         <v>79044</v>
@@ -4320,10 +4320,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>559539</v>
+        <v>559572</v>
       </c>
       <c r="R37" t="n">
-        <v>7064049</v>
+        <v>7064054</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4382,10 +4382,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129427248</v>
+        <v>129427278</v>
       </c>
       <c r="B38" t="n">
-        <v>91504</v>
+        <v>79044</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4393,21 +4393,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>112</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4417,10 +4417,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>559581</v>
+        <v>559539</v>
       </c>
       <c r="R38" t="n">
-        <v>7064041</v>
+        <v>7064049</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>

--- a/artfynd/A 29563-2025 artfynd.xlsx
+++ b/artfynd/A 29563-2025 artfynd.xlsx
@@ -1190,45 +1190,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129401658</v>
+        <v>129410985</v>
       </c>
       <c r="B7" t="n">
-        <v>79044</v>
+        <v>97598</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>559658</v>
+        <v>559661</v>
       </c>
       <c r="R7" t="n">
-        <v>7063991</v>
+        <v>7063971</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1258,19 +1258,9 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>11:59</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>11:59</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1285,57 +1275,66 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129410985</v>
+        <v>129402383</v>
       </c>
       <c r="B8" t="n">
-        <v>97598</v>
+        <v>98727</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>559661</v>
+        <v>559592</v>
       </c>
       <c r="R8" t="n">
-        <v>7063971</v>
+        <v>7064059</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1365,9 +1364,19 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>12:27</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1382,66 +1391,57 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129402383</v>
+        <v>129401658</v>
       </c>
       <c r="B9" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>559592</v>
+        <v>559658</v>
       </c>
       <c r="R9" t="n">
-        <v>7064059</v>
+        <v>7063991</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1483,7 +1483,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1498,12 +1498,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1927,45 +1927,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129427236</v>
+        <v>129425867</v>
       </c>
       <c r="B14" t="n">
-        <v>91517</v>
+        <v>79044</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Mattismyrberget, Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>559485</v>
+        <v>559534</v>
       </c>
       <c r="R14" t="n">
-        <v>7064097</v>
+        <v>7064000</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1995,9 +1995,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>15:23</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2012,57 +2022,57 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129425867</v>
+        <v>129427236</v>
       </c>
       <c r="B15" t="n">
-        <v>79044</v>
+        <v>91517</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Mattismyrberget, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>559534</v>
+        <v>559485</v>
       </c>
       <c r="R15" t="n">
-        <v>7064000</v>
+        <v>7064097</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2092,19 +2102,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>15:23</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>15:23</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2119,12 +2119,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2739,10 +2739,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129427255</v>
+        <v>129425250</v>
       </c>
       <c r="B22" t="n">
-        <v>91851</v>
+        <v>57724</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2750,34 +2750,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Mattismyrberget, Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>559572</v>
+        <v>559469</v>
       </c>
       <c r="R22" t="n">
-        <v>7064006</v>
+        <v>7064105</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2807,9 +2812,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2824,22 +2839,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129425250</v>
+        <v>129427255</v>
       </c>
       <c r="B23" t="n">
-        <v>57724</v>
+        <v>91851</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2847,39 +2862,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Mattismyrberget, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>559469</v>
+        <v>559572</v>
       </c>
       <c r="R23" t="n">
-        <v>7064105</v>
+        <v>7064006</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2909,19 +2919,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>14:40</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>14:40</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2936,12 +2936,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>

--- a/artfynd/A 29563-2025 artfynd.xlsx
+++ b/artfynd/A 29563-2025 artfynd.xlsx
@@ -1190,45 +1190,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129410985</v>
+        <v>129401658</v>
       </c>
       <c r="B7" t="n">
-        <v>97598</v>
+        <v>79044</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>559661</v>
+        <v>559658</v>
       </c>
       <c r="R7" t="n">
-        <v>7063971</v>
+        <v>7063991</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1258,9 +1258,19 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1275,12 +1285,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1403,45 +1413,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129401658</v>
+        <v>129410985</v>
       </c>
       <c r="B9" t="n">
-        <v>79044</v>
+        <v>97598</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>559658</v>
+        <v>559661</v>
       </c>
       <c r="R9" t="n">
-        <v>7063991</v>
+        <v>7063971</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1471,19 +1481,9 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>11:59</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>11:59</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1498,12 +1498,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1927,45 +1927,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129425867</v>
+        <v>129427236</v>
       </c>
       <c r="B14" t="n">
-        <v>79044</v>
+        <v>91517</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Mattismyrberget, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>559534</v>
+        <v>559485</v>
       </c>
       <c r="R14" t="n">
-        <v>7064000</v>
+        <v>7064097</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1995,19 +1995,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>15:23</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>15:23</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2022,57 +2012,57 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129427236</v>
+        <v>129425867</v>
       </c>
       <c r="B15" t="n">
-        <v>91517</v>
+        <v>79044</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Mattismyrberget, Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>559485</v>
+        <v>559534</v>
       </c>
       <c r="R15" t="n">
-        <v>7064097</v>
+        <v>7064000</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2102,9 +2092,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>15:23</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2119,12 +2119,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2341,32 +2341,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129427262</v>
+        <v>129427253</v>
       </c>
       <c r="B18" t="n">
-        <v>80149</v>
+        <v>92006</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2376,10 +2376,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>559585</v>
+        <v>559571</v>
       </c>
       <c r="R18" t="n">
-        <v>7064050</v>
+        <v>7064007</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2438,10 +2438,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129427230</v>
+        <v>129427262</v>
       </c>
       <c r="B19" t="n">
-        <v>83012</v>
+        <v>80149</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2449,21 +2449,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2473,10 +2473,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>559425</v>
+        <v>559585</v>
       </c>
       <c r="R19" t="n">
-        <v>7064125</v>
+        <v>7064050</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2535,32 +2535,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129427253</v>
+        <v>129427230</v>
       </c>
       <c r="B20" t="n">
-        <v>92006</v>
+        <v>83012</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1209</v>
+        <v>6440</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2570,10 +2570,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>559571</v>
+        <v>559425</v>
       </c>
       <c r="R20" t="n">
-        <v>7064007</v>
+        <v>7064125</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3765,10 +3765,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129424669</v>
+        <v>129424832</v>
       </c>
       <c r="B32" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3776,21 +3776,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3800,10 +3800,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>559441</v>
+        <v>559430</v>
       </c>
       <c r="R32" t="n">
-        <v>7064183</v>
+        <v>7064092</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3835,7 +3835,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3845,7 +3845,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:16</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3872,10 +3877,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129424832</v>
+        <v>129424669</v>
       </c>
       <c r="B33" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3883,21 +3888,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3907,10 +3912,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>559430</v>
+        <v>559441</v>
       </c>
       <c r="R33" t="n">
-        <v>7064092</v>
+        <v>7064183</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3942,7 +3947,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -3952,12 +3957,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:16</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>På björk</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4188,10 +4188,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129427248</v>
+        <v>129427276</v>
       </c>
       <c r="B36" t="n">
-        <v>91504</v>
+        <v>79044</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4199,21 +4199,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>112</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4223,10 +4223,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>559581</v>
+        <v>559572</v>
       </c>
       <c r="R36" t="n">
-        <v>7064041</v>
+        <v>7064054</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4285,7 +4285,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129427276</v>
+        <v>129427278</v>
       </c>
       <c r="B37" t="n">
         <v>79044</v>
@@ -4320,10 +4320,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>559572</v>
+        <v>559539</v>
       </c>
       <c r="R37" t="n">
-        <v>7064054</v>
+        <v>7064049</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4382,10 +4382,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129427278</v>
+        <v>129424688</v>
       </c>
       <c r="B38" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4393,34 +4393,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Mattismyrberget, Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>559539</v>
+        <v>559466</v>
       </c>
       <c r="R38" t="n">
-        <v>7064049</v>
+        <v>7064165</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4450,9 +4455,24 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4467,22 +4487,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129424688</v>
+        <v>129427248</v>
       </c>
       <c r="B39" t="n">
-        <v>57727</v>
+        <v>91504</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4490,39 +4510,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>112</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Mattismyrberget, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>559466</v>
+        <v>559581</v>
       </c>
       <c r="R39" t="n">
-        <v>7064165</v>
+        <v>7064041</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4552,24 +4567,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>14:03</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>14:03</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4584,12 +4584,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>

--- a/artfynd/A 29563-2025 artfynd.xlsx
+++ b/artfynd/A 29563-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129402177</v>
       </c>
       <c r="B2" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>129411006</v>
       </c>
       <c r="B3" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>129402269</v>
       </c>
       <c r="B4" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>129410971</v>
       </c>
       <c r="B5" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>129410999</v>
       </c>
       <c r="B6" t="n">
-        <v>82995</v>
+        <v>83022</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>129401658</v>
       </c>
       <c r="B7" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         <v>129402383</v>
       </c>
       <c r="B8" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>129410985</v>
       </c>
       <c r="B9" t="n">
-        <v>97598</v>
+        <v>97627</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
         <v>129410986</v>
       </c>
       <c r="B10" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>129411009</v>
       </c>
       <c r="B11" t="n">
-        <v>80184</v>
+        <v>80210</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>129410992</v>
       </c>
       <c r="B12" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         <v>129425378</v>
       </c>
       <c r="B13" t="n">
-        <v>92006</v>
+        <v>92034</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
         <v>129427236</v>
       </c>
       <c r="B14" t="n">
-        <v>91517</v>
+        <v>91545</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2024,10 +2024,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129425867</v>
+        <v>129425271</v>
       </c>
       <c r="B15" t="n">
-        <v>79044</v>
+        <v>91601</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2035,23 +2035,19 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2059,10 +2055,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>559534</v>
+        <v>559486</v>
       </c>
       <c r="R15" t="n">
-        <v>7064000</v>
+        <v>7064108</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2094,7 +2090,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2104,7 +2100,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2131,10 +2127,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129425271</v>
+        <v>129425867</v>
       </c>
       <c r="B16" t="n">
-        <v>91573</v>
+        <v>79070</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2142,19 +2138,23 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2162,10 +2162,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>559486</v>
+        <v>559534</v>
       </c>
       <c r="R16" t="n">
-        <v>7064108</v>
+        <v>7064000</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2197,7 +2197,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2207,7 +2207,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2237,7 +2237,7 @@
         <v>129425134</v>
       </c>
       <c r="B17" t="n">
-        <v>82878</v>
+        <v>82905</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
         <v>129427253</v>
       </c>
       <c r="B18" t="n">
-        <v>92006</v>
+        <v>92034</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2438,10 +2438,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129427262</v>
+        <v>129427230</v>
       </c>
       <c r="B19" t="n">
-        <v>80149</v>
+        <v>83039</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2449,21 +2449,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2473,10 +2473,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>559585</v>
+        <v>559425</v>
       </c>
       <c r="R19" t="n">
-        <v>7064050</v>
+        <v>7064125</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2535,10 +2535,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129427230</v>
+        <v>129427262</v>
       </c>
       <c r="B20" t="n">
-        <v>83012</v>
+        <v>80175</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2546,21 +2546,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2570,10 +2570,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>559425</v>
+        <v>559585</v>
       </c>
       <c r="R20" t="n">
-        <v>7064125</v>
+        <v>7064050</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2635,7 +2635,7 @@
         <v>129425894</v>
       </c>
       <c r="B21" t="n">
-        <v>82878</v>
+        <v>82905</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2739,10 +2739,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129425250</v>
+        <v>129427255</v>
       </c>
       <c r="B22" t="n">
-        <v>57724</v>
+        <v>91879</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2750,39 +2750,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Mattismyrberget, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>559469</v>
+        <v>559572</v>
       </c>
       <c r="R22" t="n">
-        <v>7064105</v>
+        <v>7064006</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2812,19 +2807,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>14:40</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>14:40</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2839,22 +2824,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129427255</v>
+        <v>129425250</v>
       </c>
       <c r="B23" t="n">
-        <v>91851</v>
+        <v>57727</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2862,34 +2847,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Mattismyrberget, Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>559572</v>
+        <v>559469</v>
       </c>
       <c r="R23" t="n">
-        <v>7064006</v>
+        <v>7064105</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2919,9 +2909,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2936,22 +2936,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129427251</v>
+        <v>129427280</v>
       </c>
       <c r="B24" t="n">
-        <v>80150</v>
+        <v>79070</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2959,21 +2959,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2983,10 +2983,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>559590</v>
+        <v>559416</v>
       </c>
       <c r="R24" t="n">
-        <v>7064053</v>
+        <v>7064119</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3045,10 +3045,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129427280</v>
+        <v>129427251</v>
       </c>
       <c r="B25" t="n">
-        <v>79044</v>
+        <v>80176</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3056,21 +3056,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3080,10 +3080,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>559416</v>
+        <v>559590</v>
       </c>
       <c r="R25" t="n">
-        <v>7064119</v>
+        <v>7064053</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3145,7 +3145,7 @@
         <v>129427261</v>
       </c>
       <c r="B26" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
         <v>129425339</v>
       </c>
       <c r="B27" t="n">
-        <v>82878</v>
+        <v>82905</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3349,7 +3349,7 @@
         <v>129425698</v>
       </c>
       <c r="B28" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3466,7 +3466,7 @@
         <v>129427281</v>
       </c>
       <c r="B29" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3563,7 +3563,7 @@
         <v>129427275</v>
       </c>
       <c r="B30" t="n">
-        <v>91573</v>
+        <v>91601</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         <v>129424796</v>
       </c>
       <c r="B31" t="n">
-        <v>56301</v>
+        <v>56304</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3768,7 +3768,7 @@
         <v>129424832</v>
       </c>
       <c r="B32" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3880,7 +3880,7 @@
         <v>129424669</v>
       </c>
       <c r="B33" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3987,7 +3987,7 @@
         <v>129427252</v>
       </c>
       <c r="B34" t="n">
-        <v>83017</v>
+        <v>83044</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4084,7 +4084,7 @@
         <v>129425714</v>
       </c>
       <c r="B35" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4188,10 +4188,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129427276</v>
+        <v>129427248</v>
       </c>
       <c r="B36" t="n">
-        <v>79044</v>
+        <v>91532</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4199,21 +4199,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>112</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4223,10 +4223,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>559572</v>
+        <v>559581</v>
       </c>
       <c r="R36" t="n">
-        <v>7064054</v>
+        <v>7064041</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4285,10 +4285,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129427278</v>
+        <v>129427276</v>
       </c>
       <c r="B37" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4320,10 +4320,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>559539</v>
+        <v>559572</v>
       </c>
       <c r="R37" t="n">
-        <v>7064049</v>
+        <v>7064054</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4382,10 +4382,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129424688</v>
+        <v>129427278</v>
       </c>
       <c r="B38" t="n">
-        <v>57727</v>
+        <v>79070</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4393,39 +4393,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Mattismyrberget, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>559466</v>
+        <v>559539</v>
       </c>
       <c r="R38" t="n">
-        <v>7064165</v>
+        <v>7064049</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4455,24 +4450,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>14:03</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>14:03</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4487,22 +4467,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129427248</v>
+        <v>129424688</v>
       </c>
       <c r="B39" t="n">
-        <v>91504</v>
+        <v>57730</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4510,34 +4490,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>112</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Mattismyrberget, Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>559581</v>
+        <v>559466</v>
       </c>
       <c r="R39" t="n">
-        <v>7064041</v>
+        <v>7064165</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4567,9 +4552,24 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4584,12 +4584,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -4599,7 +4599,7 @@
         <v>129546496</v>
       </c>
       <c r="B40" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 29563-2025 artfynd.xlsx
+++ b/artfynd/A 29563-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129402177</v>
       </c>
       <c r="B2" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>129411006</v>
       </c>
       <c r="B3" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>129402269</v>
       </c>
       <c r="B4" t="n">
-        <v>80175</v>
+        <v>80180</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>129410971</v>
       </c>
       <c r="B5" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>129410999</v>
       </c>
       <c r="B6" t="n">
-        <v>83022</v>
+        <v>83027</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>129401658</v>
       </c>
       <c r="B7" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         <v>129402383</v>
       </c>
       <c r="B8" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>129410985</v>
       </c>
       <c r="B9" t="n">
-        <v>97627</v>
+        <v>97639</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
         <v>129410986</v>
       </c>
       <c r="B10" t="n">
-        <v>80175</v>
+        <v>80180</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>129411009</v>
       </c>
       <c r="B11" t="n">
-        <v>80210</v>
+        <v>80215</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>129410992</v>
       </c>
       <c r="B12" t="n">
-        <v>80175</v>
+        <v>80180</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         <v>129425378</v>
       </c>
       <c r="B13" t="n">
-        <v>92034</v>
+        <v>92040</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1927,45 +1927,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129427236</v>
+        <v>129425867</v>
       </c>
       <c r="B14" t="n">
-        <v>91545</v>
+        <v>79075</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Mattismyrberget, Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>559485</v>
+        <v>559534</v>
       </c>
       <c r="R14" t="n">
-        <v>7064097</v>
+        <v>7064000</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1995,9 +1995,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>15:23</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2012,53 +2022,57 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129425271</v>
+        <v>129427236</v>
       </c>
       <c r="B15" t="n">
-        <v>91601</v>
+        <v>91551</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Mattismyrberget, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>559486</v>
+        <v>559485</v>
       </c>
       <c r="R15" t="n">
-        <v>7064108</v>
+        <v>7064097</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2088,19 +2102,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>14:44</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>14:44</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2115,22 +2119,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129425867</v>
+        <v>129425271</v>
       </c>
       <c r="B16" t="n">
-        <v>79070</v>
+        <v>91607</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2138,23 +2142,19 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2162,10 +2162,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>559534</v>
+        <v>559486</v>
       </c>
       <c r="R16" t="n">
-        <v>7064000</v>
+        <v>7064108</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2197,7 +2197,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2207,7 +2207,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2237,7 +2237,7 @@
         <v>129425134</v>
       </c>
       <c r="B17" t="n">
-        <v>82905</v>
+        <v>82910</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
         <v>129427253</v>
       </c>
       <c r="B18" t="n">
-        <v>92034</v>
+        <v>92040</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2438,10 +2438,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129427230</v>
+        <v>129427262</v>
       </c>
       <c r="B19" t="n">
-        <v>83039</v>
+        <v>80180</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2449,21 +2449,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2473,10 +2473,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>559425</v>
+        <v>559585</v>
       </c>
       <c r="R19" t="n">
-        <v>7064125</v>
+        <v>7064050</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2535,10 +2535,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129427262</v>
+        <v>129427230</v>
       </c>
       <c r="B20" t="n">
-        <v>80175</v>
+        <v>83044</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2546,21 +2546,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2570,10 +2570,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>559585</v>
+        <v>559425</v>
       </c>
       <c r="R20" t="n">
-        <v>7064050</v>
+        <v>7064125</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2635,7 +2635,7 @@
         <v>129425894</v>
       </c>
       <c r="B21" t="n">
-        <v>82905</v>
+        <v>82910</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2742,7 +2742,7 @@
         <v>129427255</v>
       </c>
       <c r="B22" t="n">
-        <v>91879</v>
+        <v>91885</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2839,7 +2839,7 @@
         <v>129425250</v>
       </c>
       <c r="B23" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2948,10 +2948,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129427280</v>
+        <v>129427251</v>
       </c>
       <c r="B24" t="n">
-        <v>79070</v>
+        <v>80181</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2959,21 +2959,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2983,10 +2983,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>559416</v>
+        <v>559590</v>
       </c>
       <c r="R24" t="n">
-        <v>7064119</v>
+        <v>7064053</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3045,10 +3045,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129427251</v>
+        <v>129427280</v>
       </c>
       <c r="B25" t="n">
-        <v>80176</v>
+        <v>79075</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3056,21 +3056,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3080,10 +3080,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>559590</v>
+        <v>559416</v>
       </c>
       <c r="R25" t="n">
-        <v>7064053</v>
+        <v>7064119</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3145,7 +3145,7 @@
         <v>129427261</v>
       </c>
       <c r="B26" t="n">
-        <v>80175</v>
+        <v>80180</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3239,10 +3239,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129425339</v>
+        <v>129425698</v>
       </c>
       <c r="B27" t="n">
-        <v>82905</v>
+        <v>57735</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3250,34 +3250,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Mattismyrberget, Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>559494</v>
+        <v>559505</v>
       </c>
       <c r="R27" t="n">
-        <v>7064095</v>
+        <v>7064062</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3309,7 +3314,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3319,7 +3324,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3346,10 +3356,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129425698</v>
+        <v>129425339</v>
       </c>
       <c r="B28" t="n">
-        <v>57730</v>
+        <v>82910</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3357,39 +3367,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Mattismyrberget, Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>559505</v>
+        <v>559494</v>
       </c>
       <c r="R28" t="n">
-        <v>7064062</v>
+        <v>7064095</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3421,7 +3426,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3431,12 +3436,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:10</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3466,7 +3466,7 @@
         <v>129427281</v>
       </c>
       <c r="B29" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3563,7 +3563,7 @@
         <v>129427275</v>
       </c>
       <c r="B30" t="n">
-        <v>91601</v>
+        <v>91607</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         <v>129424796</v>
       </c>
       <c r="B31" t="n">
-        <v>56304</v>
+        <v>56309</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3765,10 +3765,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129424832</v>
+        <v>129424669</v>
       </c>
       <c r="B32" t="n">
-        <v>80175</v>
+        <v>79075</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3776,21 +3776,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3800,10 +3800,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>559430</v>
+        <v>559441</v>
       </c>
       <c r="R32" t="n">
-        <v>7064092</v>
+        <v>7064183</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3835,7 +3835,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3845,12 +3845,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:16</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>På björk</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3877,10 +3872,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129424669</v>
+        <v>129424832</v>
       </c>
       <c r="B33" t="n">
-        <v>79070</v>
+        <v>80180</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3888,21 +3883,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3912,10 +3907,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>559441</v>
+        <v>559430</v>
       </c>
       <c r="R33" t="n">
-        <v>7064183</v>
+        <v>7064092</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3947,7 +3942,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -3957,7 +3952,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:16</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3987,7 +3987,7 @@
         <v>129427252</v>
       </c>
       <c r="B34" t="n">
-        <v>83044</v>
+        <v>83049</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4084,7 +4084,7 @@
         <v>129425714</v>
       </c>
       <c r="B35" t="n">
-        <v>80175</v>
+        <v>80180</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4188,10 +4188,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129427248</v>
+        <v>129427276</v>
       </c>
       <c r="B36" t="n">
-        <v>91532</v>
+        <v>79075</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4199,21 +4199,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>112</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4223,10 +4223,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>559581</v>
+        <v>559572</v>
       </c>
       <c r="R36" t="n">
-        <v>7064041</v>
+        <v>7064054</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4285,10 +4285,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129427276</v>
+        <v>129427278</v>
       </c>
       <c r="B37" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4320,10 +4320,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>559572</v>
+        <v>559539</v>
       </c>
       <c r="R37" t="n">
-        <v>7064054</v>
+        <v>7064049</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4382,10 +4382,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129427278</v>
+        <v>129424688</v>
       </c>
       <c r="B38" t="n">
-        <v>79070</v>
+        <v>57735</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4393,34 +4393,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Mattismyrberget, Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>559539</v>
+        <v>559466</v>
       </c>
       <c r="R38" t="n">
-        <v>7064049</v>
+        <v>7064165</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4450,9 +4455,24 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4467,22 +4487,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129424688</v>
+        <v>129427248</v>
       </c>
       <c r="B39" t="n">
-        <v>57730</v>
+        <v>91538</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4490,39 +4510,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>112</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Mattismyrberget, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>559466</v>
+        <v>559581</v>
       </c>
       <c r="R39" t="n">
-        <v>7064165</v>
+        <v>7064041</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4552,24 +4567,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>14:03</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>14:03</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4584,12 +4584,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -4599,7 +4599,7 @@
         <v>129546496</v>
       </c>
       <c r="B40" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 29563-2025 artfynd.xlsx
+++ b/artfynd/A 29563-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129402177</v>
       </c>
       <c r="B2" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>129411006</v>
       </c>
       <c r="B3" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>129402269</v>
       </c>
       <c r="B4" t="n">
-        <v>80180</v>
+        <v>80181</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>129410971</v>
       </c>
       <c r="B5" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>129410999</v>
       </c>
       <c r="B6" t="n">
-        <v>83027</v>
+        <v>83028</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>129401658</v>
       </c>
       <c r="B7" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         <v>129402383</v>
       </c>
       <c r="B8" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>129410985</v>
       </c>
       <c r="B9" t="n">
-        <v>97639</v>
+        <v>97640</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
         <v>129410986</v>
       </c>
       <c r="B10" t="n">
-        <v>80180</v>
+        <v>80181</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>129411009</v>
       </c>
       <c r="B11" t="n">
-        <v>80215</v>
+        <v>80216</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>129410992</v>
       </c>
       <c r="B12" t="n">
-        <v>80180</v>
+        <v>80181</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         <v>129425378</v>
       </c>
       <c r="B13" t="n">
-        <v>92040</v>
+        <v>92041</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1927,45 +1927,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129425867</v>
+        <v>129427236</v>
       </c>
       <c r="B14" t="n">
-        <v>79075</v>
+        <v>91552</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Mattismyrberget, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>559534</v>
+        <v>559485</v>
       </c>
       <c r="R14" t="n">
-        <v>7064000</v>
+        <v>7064097</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1995,19 +1995,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>15:23</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>15:23</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2022,57 +2012,57 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129427236</v>
+        <v>129425867</v>
       </c>
       <c r="B15" t="n">
-        <v>91551</v>
+        <v>79076</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Mattismyrberget, Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>559485</v>
+        <v>559534</v>
       </c>
       <c r="R15" t="n">
-        <v>7064097</v>
+        <v>7064000</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2102,9 +2092,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>15:23</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2119,12 +2119,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2134,7 +2134,7 @@
         <v>129425271</v>
       </c>
       <c r="B16" t="n">
-        <v>91607</v>
+        <v>91608</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
         <v>129425134</v>
       </c>
       <c r="B17" t="n">
-        <v>82910</v>
+        <v>82911</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
         <v>129427253</v>
       </c>
       <c r="B18" t="n">
-        <v>92040</v>
+        <v>92041</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2441,7 +2441,7 @@
         <v>129427262</v>
       </c>
       <c r="B19" t="n">
-        <v>80180</v>
+        <v>80181</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>129427230</v>
       </c>
       <c r="B20" t="n">
-        <v>83044</v>
+        <v>83045</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2635,7 +2635,7 @@
         <v>129425894</v>
       </c>
       <c r="B21" t="n">
-        <v>82910</v>
+        <v>82911</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2742,7 +2742,7 @@
         <v>129427255</v>
       </c>
       <c r="B22" t="n">
-        <v>91885</v>
+        <v>91886</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2839,7 +2839,7 @@
         <v>129425250</v>
       </c>
       <c r="B23" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2951,7 +2951,7 @@
         <v>129427251</v>
       </c>
       <c r="B24" t="n">
-        <v>80181</v>
+        <v>80182</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3048,7 +3048,7 @@
         <v>129427280</v>
       </c>
       <c r="B25" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3145,7 +3145,7 @@
         <v>129427261</v>
       </c>
       <c r="B26" t="n">
-        <v>80180</v>
+        <v>80181</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3239,10 +3239,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129425698</v>
+        <v>129425339</v>
       </c>
       <c r="B27" t="n">
-        <v>57735</v>
+        <v>82911</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3250,39 +3250,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Mattismyrberget, Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>559505</v>
+        <v>559494</v>
       </c>
       <c r="R27" t="n">
-        <v>7064062</v>
+        <v>7064095</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3314,7 +3309,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3324,12 +3319,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:10</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3356,10 +3346,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129425339</v>
+        <v>129425698</v>
       </c>
       <c r="B28" t="n">
-        <v>82910</v>
+        <v>57736</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3367,34 +3357,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Mattismyrberget, Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>559494</v>
+        <v>559505</v>
       </c>
       <c r="R28" t="n">
-        <v>7064095</v>
+        <v>7064062</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3426,7 +3421,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3436,7 +3431,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3466,7 +3466,7 @@
         <v>129427281</v>
       </c>
       <c r="B29" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3563,7 +3563,7 @@
         <v>129427275</v>
       </c>
       <c r="B30" t="n">
-        <v>91607</v>
+        <v>91608</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         <v>129424796</v>
       </c>
       <c r="B31" t="n">
-        <v>56309</v>
+        <v>56310</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3768,7 +3768,7 @@
         <v>129424669</v>
       </c>
       <c r="B32" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3875,7 +3875,7 @@
         <v>129424832</v>
       </c>
       <c r="B33" t="n">
-        <v>80180</v>
+        <v>80181</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3987,7 +3987,7 @@
         <v>129427252</v>
       </c>
       <c r="B34" t="n">
-        <v>83049</v>
+        <v>83050</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4084,7 +4084,7 @@
         <v>129425714</v>
       </c>
       <c r="B35" t="n">
-        <v>80180</v>
+        <v>80181</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4188,10 +4188,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129427276</v>
+        <v>129427248</v>
       </c>
       <c r="B36" t="n">
-        <v>79075</v>
+        <v>91539</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4199,21 +4199,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>112</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4223,10 +4223,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>559572</v>
+        <v>559581</v>
       </c>
       <c r="R36" t="n">
-        <v>7064054</v>
+        <v>7064041</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4285,10 +4285,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129427278</v>
+        <v>129427276</v>
       </c>
       <c r="B37" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4320,10 +4320,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>559539</v>
+        <v>559572</v>
       </c>
       <c r="R37" t="n">
-        <v>7064049</v>
+        <v>7064054</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4382,10 +4382,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129424688</v>
+        <v>129427278</v>
       </c>
       <c r="B38" t="n">
-        <v>57735</v>
+        <v>79076</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4393,39 +4393,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Mattismyrberget, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>559466</v>
+        <v>559539</v>
       </c>
       <c r="R38" t="n">
-        <v>7064165</v>
+        <v>7064049</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4455,24 +4450,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>14:03</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>14:03</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4487,22 +4467,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129427248</v>
+        <v>129424688</v>
       </c>
       <c r="B39" t="n">
-        <v>91538</v>
+        <v>57736</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4510,34 +4490,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>112</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Mattismyrberget, Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>559581</v>
+        <v>559466</v>
       </c>
       <c r="R39" t="n">
-        <v>7064041</v>
+        <v>7064165</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4567,9 +4552,24 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4584,12 +4584,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -4599,7 +4599,7 @@
         <v>129546496</v>
       </c>
       <c r="B40" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 29563-2025 artfynd.xlsx
+++ b/artfynd/A 29563-2025 artfynd.xlsx
@@ -2948,10 +2948,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129427251</v>
+        <v>129427280</v>
       </c>
       <c r="B24" t="n">
-        <v>80182</v>
+        <v>79076</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2959,21 +2959,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2983,10 +2983,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>559590</v>
+        <v>559416</v>
       </c>
       <c r="R24" t="n">
-        <v>7064053</v>
+        <v>7064119</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3045,10 +3045,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129427280</v>
+        <v>129427251</v>
       </c>
       <c r="B25" t="n">
-        <v>79076</v>
+        <v>80182</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3056,21 +3056,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3080,10 +3080,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>559416</v>
+        <v>559590</v>
       </c>
       <c r="R25" t="n">
-        <v>7064119</v>
+        <v>7064053</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>

--- a/artfynd/A 29563-2025 artfynd.xlsx
+++ b/artfynd/A 29563-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129402177</v>
       </c>
       <c r="B2" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>129411006</v>
       </c>
       <c r="B3" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>129402269</v>
       </c>
       <c r="B4" t="n">
-        <v>80181</v>
+        <v>80186</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>129410999</v>
       </c>
       <c r="B6" t="n">
-        <v>83028</v>
+        <v>83033</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1190,45 +1190,54 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129401658</v>
+        <v>129402383</v>
       </c>
       <c r="B7" t="n">
-        <v>79076</v>
+        <v>98774</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>559658</v>
+        <v>559592</v>
       </c>
       <c r="R7" t="n">
-        <v>7063991</v>
+        <v>7064059</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1260,7 +1269,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1270,7 +1279,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1285,66 +1294,57 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129402383</v>
+        <v>129410985</v>
       </c>
       <c r="B8" t="n">
-        <v>98769</v>
+        <v>97645</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>559592</v>
+        <v>559661</v>
       </c>
       <c r="R8" t="n">
-        <v>7064059</v>
+        <v>7063971</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1374,19 +1374,9 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>12:27</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>12:27</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1401,57 +1391,57 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129410985</v>
+        <v>129401658</v>
       </c>
       <c r="B9" t="n">
-        <v>97640</v>
+        <v>79081</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>559661</v>
+        <v>559658</v>
       </c>
       <c r="R9" t="n">
-        <v>7063971</v>
+        <v>7063991</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1481,9 +1471,19 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1498,12 +1498,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1513,7 +1513,7 @@
         <v>129410986</v>
       </c>
       <c r="B10" t="n">
-        <v>80181</v>
+        <v>80186</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>129411009</v>
       </c>
       <c r="B11" t="n">
-        <v>80216</v>
+        <v>80221</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>129410992</v>
       </c>
       <c r="B12" t="n">
-        <v>80181</v>
+        <v>80186</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         <v>129425378</v>
       </c>
       <c r="B13" t="n">
-        <v>92041</v>
+        <v>92046</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1927,45 +1927,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129427236</v>
+        <v>129425867</v>
       </c>
       <c r="B14" t="n">
-        <v>91552</v>
+        <v>79081</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Mattismyrberget, Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>559485</v>
+        <v>559534</v>
       </c>
       <c r="R14" t="n">
-        <v>7064097</v>
+        <v>7064000</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1995,9 +1995,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>15:23</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2012,57 +2022,57 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129425867</v>
+        <v>129427236</v>
       </c>
       <c r="B15" t="n">
-        <v>79076</v>
+        <v>91557</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Mattismyrberget, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>559534</v>
+        <v>559485</v>
       </c>
       <c r="R15" t="n">
-        <v>7064000</v>
+        <v>7064097</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2092,19 +2102,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>15:23</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>15:23</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2119,12 +2119,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2134,7 +2134,7 @@
         <v>129425271</v>
       </c>
       <c r="B16" t="n">
-        <v>91608</v>
+        <v>91613</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
         <v>129425134</v>
       </c>
       <c r="B17" t="n">
-        <v>82911</v>
+        <v>82916</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
         <v>129427253</v>
       </c>
       <c r="B18" t="n">
-        <v>92041</v>
+        <v>92046</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2441,7 +2441,7 @@
         <v>129427262</v>
       </c>
       <c r="B19" t="n">
-        <v>80181</v>
+        <v>80186</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>129427230</v>
       </c>
       <c r="B20" t="n">
-        <v>83045</v>
+        <v>83050</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2635,7 +2635,7 @@
         <v>129425894</v>
       </c>
       <c r="B21" t="n">
-        <v>82911</v>
+        <v>82916</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2742,7 +2742,7 @@
         <v>129427255</v>
       </c>
       <c r="B22" t="n">
-        <v>91886</v>
+        <v>91891</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2948,10 +2948,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129427280</v>
+        <v>129427251</v>
       </c>
       <c r="B24" t="n">
-        <v>79076</v>
+        <v>80187</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2959,21 +2959,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2983,10 +2983,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>559416</v>
+        <v>559590</v>
       </c>
       <c r="R24" t="n">
-        <v>7064119</v>
+        <v>7064053</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3045,10 +3045,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129427251</v>
+        <v>129427280</v>
       </c>
       <c r="B25" t="n">
-        <v>80182</v>
+        <v>79081</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3056,21 +3056,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3080,10 +3080,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>559590</v>
+        <v>559416</v>
       </c>
       <c r="R25" t="n">
-        <v>7064053</v>
+        <v>7064119</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3145,7 +3145,7 @@
         <v>129427261</v>
       </c>
       <c r="B26" t="n">
-        <v>80181</v>
+        <v>80186</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
         <v>129425339</v>
       </c>
       <c r="B27" t="n">
-        <v>82911</v>
+        <v>82916</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3466,7 +3466,7 @@
         <v>129427281</v>
       </c>
       <c r="B29" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3563,7 +3563,7 @@
         <v>129427275</v>
       </c>
       <c r="B30" t="n">
-        <v>91608</v>
+        <v>91613</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3768,7 +3768,7 @@
         <v>129424669</v>
       </c>
       <c r="B32" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3875,7 +3875,7 @@
         <v>129424832</v>
       </c>
       <c r="B33" t="n">
-        <v>80181</v>
+        <v>80186</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3987,7 +3987,7 @@
         <v>129427252</v>
       </c>
       <c r="B34" t="n">
-        <v>83050</v>
+        <v>83055</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4084,7 +4084,7 @@
         <v>129425714</v>
       </c>
       <c r="B35" t="n">
-        <v>80181</v>
+        <v>80186</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4188,10 +4188,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129427248</v>
+        <v>129424688</v>
       </c>
       <c r="B36" t="n">
-        <v>91539</v>
+        <v>57736</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4199,34 +4199,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>112</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Mattismyrberget, Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>559581</v>
+        <v>559466</v>
       </c>
       <c r="R36" t="n">
-        <v>7064041</v>
+        <v>7064165</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4256,9 +4261,24 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4273,22 +4293,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129427276</v>
+        <v>129427248</v>
       </c>
       <c r="B37" t="n">
-        <v>79076</v>
+        <v>91544</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4296,21 +4316,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>112</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4320,10 +4340,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>559572</v>
+        <v>559581</v>
       </c>
       <c r="R37" t="n">
-        <v>7064054</v>
+        <v>7064041</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4382,10 +4402,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129427278</v>
+        <v>129427276</v>
       </c>
       <c r="B38" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4417,10 +4437,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>559539</v>
+        <v>559572</v>
       </c>
       <c r="R38" t="n">
-        <v>7064049</v>
+        <v>7064054</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4479,10 +4499,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129424688</v>
+        <v>129427278</v>
       </c>
       <c r="B39" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4490,39 +4510,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Mattismyrberget, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>559466</v>
+        <v>559539</v>
       </c>
       <c r="R39" t="n">
-        <v>7064165</v>
+        <v>7064049</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4552,24 +4567,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>14:03</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>14:03</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4584,12 +4584,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -4599,7 +4599,7 @@
         <v>129546496</v>
       </c>
       <c r="B40" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 29563-2025 artfynd.xlsx
+++ b/artfynd/A 29563-2025 artfynd.xlsx
@@ -1190,54 +1190,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129402383</v>
+        <v>129401658</v>
       </c>
       <c r="B7" t="n">
-        <v>98774</v>
+        <v>79081</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>559592</v>
+        <v>559658</v>
       </c>
       <c r="R7" t="n">
-        <v>7064059</v>
+        <v>7063991</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1269,7 +1260,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1279,7 +1270,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1294,57 +1285,66 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129410985</v>
+        <v>129402383</v>
       </c>
       <c r="B8" t="n">
-        <v>97645</v>
+        <v>98774</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>559661</v>
+        <v>559592</v>
       </c>
       <c r="R8" t="n">
-        <v>7063971</v>
+        <v>7064059</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1374,9 +1374,19 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>12:27</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1391,57 +1401,57 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129401658</v>
+        <v>129410985</v>
       </c>
       <c r="B9" t="n">
-        <v>79081</v>
+        <v>97645</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>559658</v>
+        <v>559661</v>
       </c>
       <c r="R9" t="n">
-        <v>7063991</v>
+        <v>7063971</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1471,19 +1481,9 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>11:59</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>11:59</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1498,12 +1498,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1927,45 +1927,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129425867</v>
+        <v>129427236</v>
       </c>
       <c r="B14" t="n">
-        <v>79081</v>
+        <v>91557</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Mattismyrberget, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>559534</v>
+        <v>559485</v>
       </c>
       <c r="R14" t="n">
-        <v>7064000</v>
+        <v>7064097</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1995,19 +1995,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>15:23</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>15:23</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2022,57 +2012,53 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129427236</v>
+        <v>129425271</v>
       </c>
       <c r="B15" t="n">
-        <v>91557</v>
+        <v>91613</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Mattismyrberget, Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>559485</v>
+        <v>559486</v>
       </c>
       <c r="R15" t="n">
-        <v>7064097</v>
+        <v>7064108</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2102,9 +2088,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>14:44</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2119,22 +2115,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129425271</v>
+        <v>129425867</v>
       </c>
       <c r="B16" t="n">
-        <v>91613</v>
+        <v>79081</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2142,19 +2138,23 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2162,10 +2162,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>559486</v>
+        <v>559534</v>
       </c>
       <c r="R16" t="n">
-        <v>7064108</v>
+        <v>7064000</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2197,7 +2197,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2207,7 +2207,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2341,32 +2341,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129427253</v>
+        <v>129427230</v>
       </c>
       <c r="B18" t="n">
-        <v>92046</v>
+        <v>83050</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1209</v>
+        <v>6440</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2376,10 +2376,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>559571</v>
+        <v>559425</v>
       </c>
       <c r="R18" t="n">
-        <v>7064007</v>
+        <v>7064125</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2438,32 +2438,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129427262</v>
+        <v>129427253</v>
       </c>
       <c r="B19" t="n">
-        <v>80186</v>
+        <v>92046</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2473,10 +2473,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>559585</v>
+        <v>559571</v>
       </c>
       <c r="R19" t="n">
-        <v>7064050</v>
+        <v>7064007</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2535,10 +2535,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129427230</v>
+        <v>129427262</v>
       </c>
       <c r="B20" t="n">
-        <v>83050</v>
+        <v>80186</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2546,21 +2546,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2570,10 +2570,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>559425</v>
+        <v>559585</v>
       </c>
       <c r="R20" t="n">
-        <v>7064125</v>
+        <v>7064050</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3765,10 +3765,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129424669</v>
+        <v>129424832</v>
       </c>
       <c r="B32" t="n">
-        <v>79081</v>
+        <v>80186</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3776,21 +3776,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3800,10 +3800,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>559441</v>
+        <v>559430</v>
       </c>
       <c r="R32" t="n">
-        <v>7064183</v>
+        <v>7064092</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3835,7 +3835,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3845,7 +3845,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:16</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3872,10 +3877,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129424832</v>
+        <v>129424669</v>
       </c>
       <c r="B33" t="n">
-        <v>80186</v>
+        <v>79081</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3883,21 +3888,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3907,10 +3912,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>559430</v>
+        <v>559441</v>
       </c>
       <c r="R33" t="n">
-        <v>7064092</v>
+        <v>7064183</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3942,7 +3947,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -3952,12 +3957,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:16</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>På björk</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4188,10 +4188,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129424688</v>
+        <v>129427248</v>
       </c>
       <c r="B36" t="n">
-        <v>57736</v>
+        <v>91544</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4199,39 +4199,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>112</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Mattismyrberget, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>559466</v>
+        <v>559581</v>
       </c>
       <c r="R36" t="n">
-        <v>7064165</v>
+        <v>7064041</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4261,24 +4256,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>14:03</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>14:03</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4293,22 +4273,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129427248</v>
+        <v>129427276</v>
       </c>
       <c r="B37" t="n">
-        <v>91544</v>
+        <v>79081</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4316,21 +4296,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>112</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4340,10 +4320,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>559581</v>
+        <v>559572</v>
       </c>
       <c r="R37" t="n">
-        <v>7064041</v>
+        <v>7064054</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4402,7 +4382,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129427276</v>
+        <v>129427278</v>
       </c>
       <c r="B38" t="n">
         <v>79081</v>
@@ -4437,10 +4417,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>559572</v>
+        <v>559539</v>
       </c>
       <c r="R38" t="n">
-        <v>7064054</v>
+        <v>7064049</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4499,10 +4479,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129427278</v>
+        <v>129424688</v>
       </c>
       <c r="B39" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4510,34 +4490,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Mattismyrberget, Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>559539</v>
+        <v>559466</v>
       </c>
       <c r="R39" t="n">
-        <v>7064049</v>
+        <v>7064165</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4567,9 +4552,24 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4584,12 +4584,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>

--- a/artfynd/A 29563-2025 artfynd.xlsx
+++ b/artfynd/A 29563-2025 artfynd.xlsx
@@ -1190,45 +1190,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129401658</v>
+        <v>129410985</v>
       </c>
       <c r="B7" t="n">
-        <v>79081</v>
+        <v>97645</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>559658</v>
+        <v>559661</v>
       </c>
       <c r="R7" t="n">
-        <v>7063991</v>
+        <v>7063971</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1258,19 +1258,9 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>11:59</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>11:59</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1285,12 +1275,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1413,45 +1403,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129410985</v>
+        <v>129401658</v>
       </c>
       <c r="B9" t="n">
-        <v>97645</v>
+        <v>79081</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>559661</v>
+        <v>559658</v>
       </c>
       <c r="R9" t="n">
-        <v>7063971</v>
+        <v>7063991</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1481,9 +1471,19 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1498,12 +1498,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -2341,32 +2341,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129427230</v>
+        <v>129427253</v>
       </c>
       <c r="B18" t="n">
-        <v>83050</v>
+        <v>92046</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6440</v>
+        <v>1209</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2376,10 +2376,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>559425</v>
+        <v>559571</v>
       </c>
       <c r="R18" t="n">
-        <v>7064125</v>
+        <v>7064007</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2438,32 +2438,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129427253</v>
+        <v>129427262</v>
       </c>
       <c r="B19" t="n">
-        <v>92046</v>
+        <v>80186</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2473,10 +2473,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>559571</v>
+        <v>559585</v>
       </c>
       <c r="R19" t="n">
-        <v>7064007</v>
+        <v>7064050</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2535,10 +2535,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129427262</v>
+        <v>129427230</v>
       </c>
       <c r="B20" t="n">
-        <v>80186</v>
+        <v>83050</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2546,21 +2546,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2570,10 +2570,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>559585</v>
+        <v>559425</v>
       </c>
       <c r="R20" t="n">
-        <v>7064050</v>
+        <v>7064125</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2739,10 +2739,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129427255</v>
+        <v>129425250</v>
       </c>
       <c r="B22" t="n">
-        <v>91891</v>
+        <v>57733</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2750,34 +2750,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Mattismyrberget, Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>559572</v>
+        <v>559469</v>
       </c>
       <c r="R22" t="n">
-        <v>7064006</v>
+        <v>7064105</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2807,9 +2812,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2824,22 +2839,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129425250</v>
+        <v>129427255</v>
       </c>
       <c r="B23" t="n">
-        <v>57733</v>
+        <v>91891</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2847,39 +2862,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Mattismyrberget, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>559469</v>
+        <v>559572</v>
       </c>
       <c r="R23" t="n">
-        <v>7064105</v>
+        <v>7064006</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2909,19 +2919,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>14:40</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>14:40</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2936,22 +2936,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129427251</v>
+        <v>129427280</v>
       </c>
       <c r="B24" t="n">
-        <v>80187</v>
+        <v>79081</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2959,21 +2959,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2983,10 +2983,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>559590</v>
+        <v>559416</v>
       </c>
       <c r="R24" t="n">
-        <v>7064053</v>
+        <v>7064119</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3045,10 +3045,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129427280</v>
+        <v>129427251</v>
       </c>
       <c r="B25" t="n">
-        <v>79081</v>
+        <v>80187</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3056,21 +3056,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3080,10 +3080,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>559416</v>
+        <v>559590</v>
       </c>
       <c r="R25" t="n">
-        <v>7064119</v>
+        <v>7064053</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3239,10 +3239,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129425339</v>
+        <v>129425698</v>
       </c>
       <c r="B27" t="n">
-        <v>82916</v>
+        <v>57736</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3250,34 +3250,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Mattismyrberget, Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>559494</v>
+        <v>559505</v>
       </c>
       <c r="R27" t="n">
-        <v>7064095</v>
+        <v>7064062</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3309,7 +3314,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3319,7 +3324,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3346,10 +3356,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129425698</v>
+        <v>129425339</v>
       </c>
       <c r="B28" t="n">
-        <v>57736</v>
+        <v>82916</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3357,39 +3367,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Mattismyrberget, Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>559505</v>
+        <v>559494</v>
       </c>
       <c r="R28" t="n">
-        <v>7064062</v>
+        <v>7064095</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3421,7 +3426,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3431,12 +3436,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:10</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3765,10 +3765,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129424832</v>
+        <v>129424669</v>
       </c>
       <c r="B32" t="n">
-        <v>80186</v>
+        <v>79081</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3776,21 +3776,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3800,10 +3800,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>559430</v>
+        <v>559441</v>
       </c>
       <c r="R32" t="n">
-        <v>7064092</v>
+        <v>7064183</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3835,7 +3835,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3845,12 +3845,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:16</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>På björk</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3877,10 +3872,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129424669</v>
+        <v>129424832</v>
       </c>
       <c r="B33" t="n">
-        <v>79081</v>
+        <v>80186</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3888,21 +3883,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3912,10 +3907,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>559441</v>
+        <v>559430</v>
       </c>
       <c r="R33" t="n">
-        <v>7064183</v>
+        <v>7064092</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3947,7 +3942,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -3957,7 +3952,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:16</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD33" t="b">

--- a/artfynd/A 29563-2025 artfynd.xlsx
+++ b/artfynd/A 29563-2025 artfynd.xlsx
@@ -1190,45 +1190,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129410985</v>
+        <v>129401658</v>
       </c>
       <c r="B7" t="n">
-        <v>97645</v>
+        <v>79081</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>559661</v>
+        <v>559658</v>
       </c>
       <c r="R7" t="n">
-        <v>7063971</v>
+        <v>7063991</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1258,9 +1258,19 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1275,66 +1285,57 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129402383</v>
+        <v>129410985</v>
       </c>
       <c r="B8" t="n">
-        <v>98774</v>
+        <v>97645</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>559592</v>
+        <v>559661</v>
       </c>
       <c r="R8" t="n">
-        <v>7064059</v>
+        <v>7063971</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1364,19 +1365,9 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>12:27</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>12:27</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1391,57 +1382,66 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129401658</v>
+        <v>129402383</v>
       </c>
       <c r="B9" t="n">
-        <v>79081</v>
+        <v>98774</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>559658</v>
+        <v>559592</v>
       </c>
       <c r="R9" t="n">
-        <v>7063991</v>
+        <v>7064059</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1483,7 +1483,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1498,12 +1498,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1927,45 +1927,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129427236</v>
+        <v>129425867</v>
       </c>
       <c r="B14" t="n">
-        <v>91557</v>
+        <v>79081</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Mattismyrberget, Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>559485</v>
+        <v>559534</v>
       </c>
       <c r="R14" t="n">
-        <v>7064097</v>
+        <v>7064000</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1995,9 +1995,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>15:23</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2012,53 +2022,57 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129425271</v>
+        <v>129427236</v>
       </c>
       <c r="B15" t="n">
-        <v>91613</v>
+        <v>91557</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Mattismyrberget, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>559486</v>
+        <v>559485</v>
       </c>
       <c r="R15" t="n">
-        <v>7064108</v>
+        <v>7064097</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2088,19 +2102,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>14:44</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>14:44</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2115,22 +2119,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129425867</v>
+        <v>129425271</v>
       </c>
       <c r="B16" t="n">
-        <v>79081</v>
+        <v>91613</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2138,23 +2142,19 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2162,10 +2162,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>559534</v>
+        <v>559486</v>
       </c>
       <c r="R16" t="n">
-        <v>7064000</v>
+        <v>7064108</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2197,7 +2197,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2207,7 +2207,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2341,32 +2341,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129427253</v>
+        <v>129427230</v>
       </c>
       <c r="B18" t="n">
-        <v>92046</v>
+        <v>83050</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1209</v>
+        <v>6440</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2376,10 +2376,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>559571</v>
+        <v>559425</v>
       </c>
       <c r="R18" t="n">
-        <v>7064007</v>
+        <v>7064125</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2535,32 +2535,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129427230</v>
+        <v>129427253</v>
       </c>
       <c r="B20" t="n">
-        <v>83050</v>
+        <v>92046</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6440</v>
+        <v>1209</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2570,10 +2570,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>559425</v>
+        <v>559571</v>
       </c>
       <c r="R20" t="n">
-        <v>7064125</v>
+        <v>7064007</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2948,10 +2948,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129427280</v>
+        <v>129427251</v>
       </c>
       <c r="B24" t="n">
-        <v>79081</v>
+        <v>80187</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2959,21 +2959,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2983,10 +2983,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>559416</v>
+        <v>559590</v>
       </c>
       <c r="R24" t="n">
-        <v>7064119</v>
+        <v>7064053</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3045,10 +3045,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129427251</v>
+        <v>129427280</v>
       </c>
       <c r="B25" t="n">
-        <v>80187</v>
+        <v>79081</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3056,21 +3056,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3080,10 +3080,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>559590</v>
+        <v>559416</v>
       </c>
       <c r="R25" t="n">
-        <v>7064053</v>
+        <v>7064119</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3239,10 +3239,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129425698</v>
+        <v>129425339</v>
       </c>
       <c r="B27" t="n">
-        <v>57736</v>
+        <v>82916</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3250,39 +3250,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Mattismyrberget, Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>559505</v>
+        <v>559494</v>
       </c>
       <c r="R27" t="n">
-        <v>7064062</v>
+        <v>7064095</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3314,7 +3309,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3324,12 +3319,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:10</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3356,10 +3346,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129425339</v>
+        <v>129425698</v>
       </c>
       <c r="B28" t="n">
-        <v>82916</v>
+        <v>57736</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3367,34 +3357,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Mattismyrberget, Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>559494</v>
+        <v>559505</v>
       </c>
       <c r="R28" t="n">
-        <v>7064095</v>
+        <v>7064062</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3426,7 +3421,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3436,7 +3431,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4188,10 +4188,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129427248</v>
+        <v>129427276</v>
       </c>
       <c r="B36" t="n">
-        <v>91544</v>
+        <v>79081</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4199,21 +4199,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>112</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4223,10 +4223,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>559581</v>
+        <v>559572</v>
       </c>
       <c r="R36" t="n">
-        <v>7064041</v>
+        <v>7064054</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4285,7 +4285,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129427276</v>
+        <v>129427278</v>
       </c>
       <c r="B37" t="n">
         <v>79081</v>
@@ -4320,10 +4320,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>559572</v>
+        <v>559539</v>
       </c>
       <c r="R37" t="n">
-        <v>7064054</v>
+        <v>7064049</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4382,10 +4382,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129427278</v>
+        <v>129424688</v>
       </c>
       <c r="B38" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4393,34 +4393,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Mattismyrberget, Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>559539</v>
+        <v>559466</v>
       </c>
       <c r="R38" t="n">
-        <v>7064049</v>
+        <v>7064165</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4450,9 +4455,24 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4467,22 +4487,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129424688</v>
+        <v>129427248</v>
       </c>
       <c r="B39" t="n">
-        <v>57736</v>
+        <v>91544</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4490,39 +4510,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>112</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Mattismyrberget, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>559466</v>
+        <v>559581</v>
       </c>
       <c r="R39" t="n">
-        <v>7064165</v>
+        <v>7064041</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4552,24 +4567,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>14:03</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>14:03</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4584,12 +4584,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>

--- a/artfynd/A 29563-2025 artfynd.xlsx
+++ b/artfynd/A 29563-2025 artfynd.xlsx
@@ -1190,45 +1190,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129401658</v>
+        <v>129410985</v>
       </c>
       <c r="B7" t="n">
-        <v>79081</v>
+        <v>97649</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>559658</v>
+        <v>559661</v>
       </c>
       <c r="R7" t="n">
-        <v>7063991</v>
+        <v>7063971</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1258,19 +1258,9 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>11:59</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>11:59</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1285,57 +1275,57 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129410985</v>
+        <v>129401658</v>
       </c>
       <c r="B8" t="n">
-        <v>97645</v>
+        <v>79081</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>559661</v>
+        <v>559658</v>
       </c>
       <c r="R8" t="n">
-        <v>7063971</v>
+        <v>7063991</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1365,9 +1355,19 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1382,12 +1382,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1397,7 +1397,7 @@
         <v>129402383</v>
       </c>
       <c r="B9" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         <v>129425378</v>
       </c>
       <c r="B13" t="n">
-        <v>92046</v>
+        <v>92050</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1927,45 +1927,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129425867</v>
+        <v>129427236</v>
       </c>
       <c r="B14" t="n">
-        <v>79081</v>
+        <v>91561</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Mattismyrberget, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>559534</v>
+        <v>559485</v>
       </c>
       <c r="R14" t="n">
-        <v>7064000</v>
+        <v>7064097</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1995,19 +1995,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>15:23</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>15:23</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2022,57 +2012,53 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129427236</v>
+        <v>129425271</v>
       </c>
       <c r="B15" t="n">
-        <v>91557</v>
+        <v>91617</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Mattismyrberget, Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>559485</v>
+        <v>559486</v>
       </c>
       <c r="R15" t="n">
-        <v>7064097</v>
+        <v>7064108</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2102,9 +2088,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>14:44</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2119,22 +2115,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129425271</v>
+        <v>129425867</v>
       </c>
       <c r="B16" t="n">
-        <v>91613</v>
+        <v>79081</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2142,19 +2138,23 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2162,10 +2162,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>559486</v>
+        <v>559534</v>
       </c>
       <c r="R16" t="n">
-        <v>7064108</v>
+        <v>7064000</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2197,7 +2197,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2207,7 +2207,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2341,32 +2341,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129427230</v>
+        <v>129427253</v>
       </c>
       <c r="B18" t="n">
-        <v>83050</v>
+        <v>92050</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6440</v>
+        <v>1209</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2376,10 +2376,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>559425</v>
+        <v>559571</v>
       </c>
       <c r="R18" t="n">
-        <v>7064125</v>
+        <v>7064007</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2535,32 +2535,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129427253</v>
+        <v>129427230</v>
       </c>
       <c r="B20" t="n">
-        <v>92046</v>
+        <v>83050</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1209</v>
+        <v>6440</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2570,10 +2570,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>559571</v>
+        <v>559425</v>
       </c>
       <c r="R20" t="n">
-        <v>7064007</v>
+        <v>7064125</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2739,10 +2739,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129425250</v>
+        <v>129427255</v>
       </c>
       <c r="B22" t="n">
-        <v>57733</v>
+        <v>91895</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2750,39 +2750,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Mattismyrberget, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>559469</v>
+        <v>559572</v>
       </c>
       <c r="R22" t="n">
-        <v>7064105</v>
+        <v>7064006</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2812,19 +2807,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>14:40</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>14:40</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2839,22 +2824,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129427255</v>
+        <v>129425250</v>
       </c>
       <c r="B23" t="n">
-        <v>91891</v>
+        <v>57733</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2862,34 +2847,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Mattismyrberget, Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>559572</v>
+        <v>559469</v>
       </c>
       <c r="R23" t="n">
-        <v>7064006</v>
+        <v>7064105</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2919,9 +2909,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2936,22 +2936,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129427251</v>
+        <v>129427280</v>
       </c>
       <c r="B24" t="n">
-        <v>80187</v>
+        <v>79081</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2959,21 +2959,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2983,10 +2983,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>559590</v>
+        <v>559416</v>
       </c>
       <c r="R24" t="n">
-        <v>7064053</v>
+        <v>7064119</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3045,10 +3045,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129427280</v>
+        <v>129427251</v>
       </c>
       <c r="B25" t="n">
-        <v>79081</v>
+        <v>80187</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3056,21 +3056,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3080,10 +3080,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>559416</v>
+        <v>559590</v>
       </c>
       <c r="R25" t="n">
-        <v>7064119</v>
+        <v>7064053</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3239,10 +3239,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129425339</v>
+        <v>129425698</v>
       </c>
       <c r="B27" t="n">
-        <v>82916</v>
+        <v>57736</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3250,34 +3250,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Mattismyrberget, Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>559494</v>
+        <v>559505</v>
       </c>
       <c r="R27" t="n">
-        <v>7064095</v>
+        <v>7064062</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3309,7 +3314,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3319,7 +3324,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3346,10 +3356,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129425698</v>
+        <v>129425339</v>
       </c>
       <c r="B28" t="n">
-        <v>57736</v>
+        <v>82916</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3357,39 +3367,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Mattismyrberget, Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>559505</v>
+        <v>559494</v>
       </c>
       <c r="R28" t="n">
-        <v>7064062</v>
+        <v>7064095</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3421,7 +3426,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3431,12 +3436,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:10</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3563,7 +3563,7 @@
         <v>129427275</v>
       </c>
       <c r="B30" t="n">
-        <v>91613</v>
+        <v>91617</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4502,7 +4502,7 @@
         <v>129427248</v>
       </c>
       <c r="B39" t="n">
-        <v>91544</v>
+        <v>91548</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4599,7 +4599,7 @@
         <v>129546496</v>
       </c>
       <c r="B40" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 29563-2025 artfynd.xlsx
+++ b/artfynd/A 29563-2025 artfynd.xlsx
@@ -1096,7 +1096,7 @@
         <v>129410999</v>
       </c>
       <c r="B6" t="n">
-        <v>83033</v>
+        <v>83035</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1190,45 +1190,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129410985</v>
+        <v>129401658</v>
       </c>
       <c r="B7" t="n">
-        <v>97649</v>
+        <v>79081</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Spångmyran, Ång</t>
+          <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>559661</v>
+        <v>559658</v>
       </c>
       <c r="R7" t="n">
-        <v>7063971</v>
+        <v>7063991</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1258,9 +1258,19 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1275,57 +1285,66 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129401658</v>
+        <v>129402383</v>
       </c>
       <c r="B8" t="n">
-        <v>79081</v>
+        <v>98780</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Spångmyran, Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>559658</v>
+        <v>559592</v>
       </c>
       <c r="R8" t="n">
-        <v>7063991</v>
+        <v>7064059</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1357,7 +1376,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1367,7 +1386,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1382,66 +1401,57 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129402383</v>
+        <v>129410985</v>
       </c>
       <c r="B9" t="n">
-        <v>98778</v>
+        <v>97651</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Spångmyran, Spångmyran, Ång</t>
+          <t>Spångmyran, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>559592</v>
+        <v>559661</v>
       </c>
       <c r="R9" t="n">
-        <v>7064059</v>
+        <v>7063971</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1471,19 +1481,9 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>12:27</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>12:27</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1498,12 +1498,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1823,7 +1823,7 @@
         <v>129425378</v>
       </c>
       <c r="B13" t="n">
-        <v>92050</v>
+        <v>92052</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
         <v>129427236</v>
       </c>
       <c r="B14" t="n">
-        <v>91561</v>
+        <v>91563</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>129425271</v>
       </c>
       <c r="B15" t="n">
-        <v>91617</v>
+        <v>91619</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
         <v>129425134</v>
       </c>
       <c r="B17" t="n">
-        <v>82916</v>
+        <v>82918</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2341,32 +2341,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129427253</v>
+        <v>129427262</v>
       </c>
       <c r="B18" t="n">
-        <v>92050</v>
+        <v>80186</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2376,10 +2376,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>559571</v>
+        <v>559585</v>
       </c>
       <c r="R18" t="n">
-        <v>7064007</v>
+        <v>7064050</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2438,10 +2438,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129427262</v>
+        <v>129427230</v>
       </c>
       <c r="B19" t="n">
-        <v>80186</v>
+        <v>83052</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2449,21 +2449,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2473,10 +2473,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>559585</v>
+        <v>559425</v>
       </c>
       <c r="R19" t="n">
-        <v>7064050</v>
+        <v>7064125</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2535,32 +2535,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129427230</v>
+        <v>129427253</v>
       </c>
       <c r="B20" t="n">
-        <v>83050</v>
+        <v>92052</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6440</v>
+        <v>1209</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2570,10 +2570,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>559425</v>
+        <v>559571</v>
       </c>
       <c r="R20" t="n">
-        <v>7064125</v>
+        <v>7064007</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2635,7 +2635,7 @@
         <v>129425894</v>
       </c>
       <c r="B21" t="n">
-        <v>82916</v>
+        <v>82918</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2739,10 +2739,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129427255</v>
+        <v>129425250</v>
       </c>
       <c r="B22" t="n">
-        <v>91895</v>
+        <v>57733</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2750,34 +2750,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Ång</t>
+          <t>Mattismyrberget, Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>559572</v>
+        <v>559469</v>
       </c>
       <c r="R22" t="n">
-        <v>7064006</v>
+        <v>7064105</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2807,9 +2812,19 @@
           <t>2025-10-30</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2824,22 +2839,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129425250</v>
+        <v>129427255</v>
       </c>
       <c r="B23" t="n">
-        <v>57733</v>
+        <v>91897</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2847,39 +2862,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Mattismyrberget, Mattismyrberget, Ång</t>
+          <t>Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>559469</v>
+        <v>559572</v>
       </c>
       <c r="R23" t="n">
-        <v>7064105</v>
+        <v>7064006</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2909,19 +2919,9 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>14:40</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>14:40</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2936,22 +2936,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129427280</v>
+        <v>129427251</v>
       </c>
       <c r="B24" t="n">
-        <v>79081</v>
+        <v>80187</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2959,21 +2959,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2983,10 +2983,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>559416</v>
+        <v>559590</v>
       </c>
       <c r="R24" t="n">
-        <v>7064119</v>
+        <v>7064053</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3045,10 +3045,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129427251</v>
+        <v>129427280</v>
       </c>
       <c r="B25" t="n">
-        <v>80187</v>
+        <v>79081</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3056,21 +3056,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3080,10 +3080,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>559590</v>
+        <v>559416</v>
       </c>
       <c r="R25" t="n">
-        <v>7064053</v>
+        <v>7064119</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3239,10 +3239,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129425698</v>
+        <v>129425339</v>
       </c>
       <c r="B27" t="n">
-        <v>57736</v>
+        <v>82918</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3250,39 +3250,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Mattismyrberget, Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>559505</v>
+        <v>559494</v>
       </c>
       <c r="R27" t="n">
-        <v>7064062</v>
+        <v>7064095</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3314,7 +3309,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3324,12 +3319,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:10</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3356,10 +3346,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129425339</v>
+        <v>129425698</v>
       </c>
       <c r="B28" t="n">
-        <v>82916</v>
+        <v>57736</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3367,34 +3357,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Mattismyrberget, Mattismyrberget, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>559494</v>
+        <v>559505</v>
       </c>
       <c r="R28" t="n">
-        <v>7064095</v>
+        <v>7064062</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3426,7 +3421,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3436,7 +3431,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3563,7 +3563,7 @@
         <v>129427275</v>
       </c>
       <c r="B30" t="n">
-        <v>91617</v>
+        <v>91619</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3987,7 +3987,7 @@
         <v>129427252</v>
       </c>
       <c r="B34" t="n">
-        <v>83055</v>
+        <v>83057</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4502,7 +4502,7 @@
         <v>129427248</v>
       </c>
       <c r="B39" t="n">
-        <v>91548</v>
+        <v>91550</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4599,7 +4599,7 @@
         <v>129546496</v>
       </c>
       <c r="B40" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 29563-2025 artfynd.xlsx
+++ b/artfynd/A 29563-2025 artfynd.xlsx
@@ -4599,7 +4599,7 @@
         <v>129546496</v>
       </c>
       <c r="B40" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 29563-2025 artfynd.xlsx
+++ b/artfynd/A 29563-2025 artfynd.xlsx
@@ -4599,7 +4599,7 @@
         <v>129546496</v>
       </c>
       <c r="B40" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
